--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南昌·TCD国潮动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 09:30-01.28 17:00</t>
+          <t>2024.01.30 10:00-01.30 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10182</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/b6mvSDAb1699949064296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>赣州·第一届异次元动漫嘉年华</t>
+          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金辉路南3号大坪明德小学体育馆2层东侧201办公室 鲲伍体育·赣州经开区综合体育馆</t>
+          <t>迎宾大道566号 荣耀国际酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 18:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>596</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79855</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/5MWMXaxx1702623107406.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/mVYKfkkX1704781887641.png</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>鹰潭·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·第三届半夏动漫展（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>站江路25号(鹰潭火车站对面) 鹰潭华盛大酒店</t>
+          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.02 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
-      </c>
-      <c r="G4" t="n">
-        <v>65</v>
+        <v>731</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80590</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HCgQUe0P1704705130296.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>高安·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>解放路15号 凤凰湖国际大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.30 10:00-01.30 17:00</t>
+          <t>2024.02.02 09:30-02.02 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣耀国际酒店</t>
+          <t>滨江西路66号 万达广场</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.03 14:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>22.33</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/mVYKfkkX1704781887641.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,40 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>赣州·第三届半夏动漫展（取消）</t>
+          <t>吉水·only one游戏动漫节</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
+          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.02 10:00-02.04 17:00</t>
+          <t>2024.02.03 09:30-02.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>731</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华</t>
+          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>解放路15号 凤凰湖国际大酒店</t>
+          <t>胜利北路208号 欧暇·地中海酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.02 09:30-02.02 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/jskcK7TB1704702009928.png</t>
         </is>
       </c>
     </row>
@@ -776,33 +776,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>437</v>
       </c>
       <c r="G9" t="n">
-        <v>22.33</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/jskcK7TB1704702009928.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>章江南大道七一九社区-北苑东侧约260米 赣州经开区第三体育馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>432</v>
+        <v>534</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>276</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>章江南大道七一九社区-北苑东侧约260米 赣州经开区第三体育馆</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>519</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="G16" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>九江·原X星X蔚蓝ONLY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>269</v>
+        <v>109</v>
       </c>
       <c r="G17" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>320</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,33 +1350,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>810</v>
       </c>
       <c r="G23" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,33 +1391,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>1355</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,33 +1432,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>72</v>
+        <v>281</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,33 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>767</v>
+        <v>293</v>
       </c>
       <c r="G26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -1514,33 +1514,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>赣州·国乙ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1345</v>
+        <v>183</v>
       </c>
       <c r="G27" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>281</v>
+        <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>283</v>
+        <v>149</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="G30" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1692,19 +1692,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
       </c>
     </row>
@@ -1714,38 +1714,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="G32" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1755,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,38 +1796,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>鹰潭·原×铁×崩only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>227</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1837,38 +1837,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1878,38 +1878,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>182</v>
+        <v>1576</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1919,38 +1919,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>218</v>
+        <v>43</v>
       </c>
       <c r="G37" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1960,38 +1960,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>236</v>
+        <v>98</v>
       </c>
       <c r="G38" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -2001,38 +2001,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1563</v>
+        <v>149</v>
       </c>
       <c r="G39" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2042,38 +2042,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>42</v>
+        <v>555</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -2083,38 +2083,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>99</v>
-      </c>
-      <c r="G41" t="n">
-        <v>30</v>
+        <v>298</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -2124,38 +2126,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>148</v>
+        <v>3237</v>
       </c>
       <c r="G42" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -2165,38 +2167,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>544</v>
+        <v>389</v>
       </c>
       <c r="G43" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -2211,33 +2213,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3135</v>
+        <v>166</v>
       </c>
       <c r="G44" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -2247,38 +2249,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>382</v>
+        <v>843</v>
       </c>
       <c r="G45" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
         </is>
       </c>
     </row>
@@ -2288,38 +2290,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="G46" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2329,118 +2331,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>816</v>
+        <v>37</v>
       </c>
       <c r="G47" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>40</v>
-      </c>
-      <c r="G48" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>34</v>
-      </c>
-      <c r="G49" t="n">
-        <v>65</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
@@ -2575,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2629,38 +2549,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南昌·TCD国潮动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 09:30-01.28 17:00</t>
+          <t>2024.01.30 10:00-01.30 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10182</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78397</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/b6mvSDAb1699949064296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -2670,38 +2590,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>赣州·第一届异次元动漫嘉年华</t>
+          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金辉路南3号大坪明德小学体育馆2层东侧201办公室 鲲伍体育·赣州经开区综合体育馆</t>
+          <t>迎宾大道566号 荣耀国际酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 18:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>596</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79855</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/5MWMXaxx1702623107406.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/mVYKfkkX1704781887641.png</t>
         </is>
       </c>
     </row>
@@ -2711,38 +2631,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>鹰潭·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·第三届半夏动漫展（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>站江路25号(鹰潭火车站对面) 鹰潭华盛大酒店</t>
+          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.02 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
-      </c>
-      <c r="G4" t="n">
-        <v>65</v>
+        <v>731</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80590</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HCgQUe0P1704705130296.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
         </is>
       </c>
     </row>
@@ -2752,38 +2674,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>高安·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>解放路15号 凤凰湖国际大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.30 10:00-01.30 17:00</t>
+          <t>2024.02.02 09:30-02.02 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
         </is>
       </c>
     </row>
@@ -2793,38 +2715,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣耀国际酒店</t>
+          <t>滨江西路66号 万达广场</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.03 14:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>22.33</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/mVYKfkkX1704781887641.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
         </is>
       </c>
     </row>
@@ -2834,40 +2756,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>赣州·第三届半夏动漫展（取消）</t>
+          <t>吉水·only one游戏动漫节</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
+          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.02 10:00-02.04 17:00</t>
+          <t>2024.02.03 09:30-02.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>731</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
         </is>
       </c>
     </row>
@@ -2877,38 +2797,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华</t>
+          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>解放路15号 凤凰湖国际大酒店</t>
+          <t>胜利北路208号 欧暇·地中海酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.02 09:30-02.02 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/jskcK7TB1704702009928.png</t>
         </is>
       </c>
     </row>
@@ -2923,33 +2843,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>437</v>
       </c>
       <c r="G9" t="n">
-        <v>22.33</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -2959,38 +2879,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -3000,38 +2920,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/jskcK7TB1704702009928.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -3041,38 +2961,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>章江南大道七一九社区-北苑东侧约260米 赣州经开区第三体育馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>432</v>
+        <v>534</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -3082,38 +3002,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -3123,38 +3043,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>276</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -3164,38 +3084,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>章江南大道七一九社区-北苑东侧约260米 赣州经开区第三体育馆</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>519</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -3205,38 +3125,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="G16" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -3246,38 +3166,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>九江·原X星X蔚蓝ONLY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>269</v>
+        <v>109</v>
       </c>
       <c r="G17" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -3287,38 +3207,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -3328,38 +3248,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>320</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -3369,38 +3289,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -3410,38 +3330,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -3451,38 +3371,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -3497,33 +3417,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>810</v>
       </c>
       <c r="G23" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -3538,33 +3458,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>1355</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -3579,33 +3499,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>72</v>
+        <v>281</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -3620,33 +3540,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>767</v>
+        <v>293</v>
       </c>
       <c r="G26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3661,33 +3581,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>赣州·国乙ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1345</v>
+        <v>183</v>
       </c>
       <c r="G27" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -3697,38 +3617,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>281</v>
+        <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -3738,38 +3658,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>283</v>
+        <v>149</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -3779,38 +3699,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="G30" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3745,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3839,19 +3759,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
       </c>
     </row>
@@ -3861,38 +3781,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="G32" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -3902,38 +3822,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -3943,38 +3863,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>鹰潭·原×铁×崩only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>227</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3984,38 +3904,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4025,38 +3945,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>182</v>
+        <v>1576</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -4066,38 +3986,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>218</v>
+        <v>43</v>
       </c>
       <c r="G37" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -4107,38 +4027,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>236</v>
+        <v>98</v>
       </c>
       <c r="G38" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -4148,38 +4068,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1563</v>
+        <v>149</v>
       </c>
       <c r="G39" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -4189,38 +4109,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>42</v>
+        <v>555</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -4230,38 +4150,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>99</v>
-      </c>
-      <c r="G41" t="n">
-        <v>30</v>
+        <v>298</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4271,38 +4193,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>148</v>
+        <v>3237</v>
       </c>
       <c r="G42" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -4312,38 +4234,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>544</v>
+        <v>389</v>
       </c>
       <c r="G43" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -4358,33 +4280,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3135</v>
+        <v>166</v>
       </c>
       <c r="G44" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -4394,38 +4316,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>382</v>
+        <v>843</v>
       </c>
       <c r="G45" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
         </is>
       </c>
     </row>
@@ -4435,38 +4357,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="G46" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -4476,118 +4398,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>816</v>
+        <v>37</v>
       </c>
       <c r="G47" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>40</v>
-      </c>
-      <c r="G48" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>34</v>
-      </c>
-      <c r="G49" t="n">
-        <v>65</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G14" t="n">
         <v>45</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>810</v>
+        <v>831</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="G24" t="n">
         <v>45</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G26" t="n">
         <v>50</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G27" t="n">
         <v>88</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G28" t="n">
         <v>45</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G29" t="n">
         <v>48</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G32" t="n">
         <v>40</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="G36" t="n">
         <v>50</v>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G39" t="n">
         <v>40</v>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3237</v>
+        <v>3329</v>
       </c>
       <c r="G42" t="n">
         <v>65</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G43" t="n">
         <v>45</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G44" t="n">
         <v>30</v>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G47" t="n">
         <v>65</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G14" t="n">
         <v>45</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="G24" t="n">
         <v>45</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G26" t="n">
         <v>50</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G27" t="n">
         <v>88</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G28" t="n">
         <v>45</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G29" t="n">
         <v>48</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G32" t="n">
         <v>40</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="G36" t="n">
         <v>50</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G39" t="n">
         <v>40</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3237</v>
+        <v>3329</v>
       </c>
       <c r="G42" t="n">
         <v>65</v>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G43" t="n">
         <v>45</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G44" t="n">
         <v>30</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G47" t="n">
         <v>65</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -554,7 +554,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/mVYKfkkX1704781887641.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/8YmblqtV1706524591857.png</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华</t>
+          <t>高安·星语动漫嘉年华（取消）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -628,8 +628,10 @@
       <c r="F5" t="n">
         <v>119</v>
       </c>
-      <c r="G5" t="n">
-        <v>40</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -667,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
         <v>22.33</v>
@@ -708,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
         <v>35</v>
@@ -749,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -761,7 +763,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/jskcK7TB1704702009928.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
         </is>
       </c>
     </row>
@@ -790,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -831,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -872,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -904,7 +906,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>章江南大道七一九社区-北苑东侧约260米 赣州经开区第三体育馆</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -913,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -954,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -995,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G14" t="n">
         <v>45</v>
@@ -1036,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1077,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -1104,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1118,10 +1120,12 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>109</v>
-      </c>
-      <c r="G17" t="n">
-        <v>50</v>
+        <v>112</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1159,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -1241,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -1268,33 +1272,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1313,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>83</v>
+        <v>857</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,33 +1354,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>831</v>
+        <v>1377</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,33 +1395,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1360</v>
+        <v>289</v>
       </c>
       <c r="G24" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,33 +1436,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,33 +1477,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>296</v>
-      </c>
-      <c r="G26" t="n">
-        <v>50</v>
+        <v>186</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1515,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="G27" t="n">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -1555,33 +1561,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="G28" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -1596,33 +1602,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="G29" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1638,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1673,38 +1679,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>鹰潭·原×铁×崩only</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>201</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1714,38 +1720,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="G32" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1761,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1801,33 +1807,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>231</v>
+        <v>1595</v>
       </c>
       <c r="G34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1837,38 +1843,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>251</v>
+        <v>47</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1878,38 +1884,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1582</v>
+        <v>98</v>
       </c>
       <c r="G36" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1919,38 +1925,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1960,38 +1966,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>98</v>
+        <v>567</v>
       </c>
       <c r="G38" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -2001,38 +2007,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>150</v>
-      </c>
-      <c r="G39" t="n">
-        <v>40</v>
+        <v>297</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -2042,38 +2050,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>559</v>
+        <v>3430</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -2083,40 +2091,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>298</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>406</v>
+      </c>
+      <c r="G41" t="n">
+        <v>45</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -2131,33 +2137,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3329</v>
+        <v>179</v>
       </c>
       <c r="G42" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -2167,38 +2173,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>392</v>
+        <v>879</v>
       </c>
       <c r="G43" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
         </is>
       </c>
     </row>
@@ -2208,38 +2214,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="G44" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -2249,38 +2255,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>858</v>
+        <v>58</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2295,33 +2301,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -2331,38 +2337,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2574,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -2609,7 +2615,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -2621,7 +2627,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/mVYKfkkX1704781887641.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/8YmblqtV1706524591857.png</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2656,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2679,7 +2685,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华</t>
+          <t>高安·星语动漫嘉年华（取消）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2695,8 +2701,10 @@
       <c r="F5" t="n">
         <v>119</v>
       </c>
-      <c r="G5" t="n">
-        <v>40</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2734,7 +2742,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
         <v>22.33</v>
@@ -2775,7 +2783,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
         <v>35</v>
@@ -2816,7 +2824,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2828,7 +2836,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/jskcK7TB1704702009928.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2865,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2898,7 +2906,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -2939,7 +2947,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -2971,7 +2979,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>章江南大道七一九社区-北苑东侧约260米 赣州经开区第三体育馆</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2980,7 +2988,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -3021,7 +3029,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -3062,7 +3070,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G14" t="n">
         <v>45</v>
@@ -3103,7 +3111,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -3144,7 +3152,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -3171,7 +3179,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3185,10 +3193,12 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>109</v>
-      </c>
-      <c r="G17" t="n">
-        <v>50</v>
+        <v>112</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3226,7 +3236,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -3308,7 +3318,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -3335,33 +3345,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -3376,33 +3386,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>83</v>
+        <v>857</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -3417,33 +3427,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>832</v>
+        <v>1377</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -3458,33 +3468,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1360</v>
+        <v>289</v>
       </c>
       <c r="G24" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -3499,33 +3509,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3540,33 +3550,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>296</v>
-      </c>
-      <c r="G26" t="n">
-        <v>50</v>
+        <v>186</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -3576,38 +3588,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="G27" t="n">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -3622,33 +3634,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="G28" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -3663,33 +3675,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="G29" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3711,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -3740,38 +3752,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>鹰潭·原×铁×崩only</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>201</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3793,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="G32" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,38 +3834,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3868,33 +3880,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>231</v>
+        <v>1595</v>
       </c>
       <c r="G34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -3904,38 +3916,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>251</v>
+        <v>47</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -3945,38 +3957,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1582</v>
+        <v>98</v>
       </c>
       <c r="G36" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -3986,38 +3998,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -4027,38 +4039,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>98</v>
+        <v>567</v>
       </c>
       <c r="G38" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -4068,38 +4080,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>150</v>
-      </c>
-      <c r="G39" t="n">
-        <v>40</v>
+        <v>297</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4109,38 +4123,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>559</v>
+        <v>3430</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -4150,40 +4164,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>298</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>406</v>
+      </c>
+      <c r="G41" t="n">
+        <v>45</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -4198,33 +4210,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3329</v>
+        <v>179</v>
       </c>
       <c r="G42" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -4234,38 +4246,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>392</v>
+        <v>879</v>
       </c>
       <c r="G43" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
         </is>
       </c>
     </row>
@@ -4275,38 +4287,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="G44" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -4316,38 +4328,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>858</v>
+        <v>58</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -4362,33 +4374,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -4398,38 +4410,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
       </c>
     </row>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -504,7 +504,7 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
         <v>22.33</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G14" t="n">
         <v>45</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1377</v>
+        <v>1385</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
         <v>40</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G33" t="n">
         <v>40</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1595</v>
+        <v>1601</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3430</v>
+        <v>3499</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -2577,7 +2577,7 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
         <v>45</v>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
         <v>22.33</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
         <v>35</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G14" t="n">
         <v>45</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1377</v>
+        <v>1385</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
         <v>40</v>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G33" t="n">
         <v>40</v>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1595</v>
+        <v>1601</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3430</v>
+        <v>3499</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>迎宾大道566号 荣耀国际酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.30 10:00-01.30 17:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/8YmblqtV1706524591857.png</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·第三届半夏动漫展（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣耀国际酒店</t>
+          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.02 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G3" t="n">
-        <v>45</v>
+        <v>732</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/8YmblqtV1706524591857.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
         </is>
       </c>
     </row>
@@ -569,21 +571,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>赣州·第三届半夏动漫展（取消）</t>
+          <t>高安·星语动漫嘉年华（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
+          <t>解放路15号 凤凰湖国际大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.02 10:00-02.04 17:00</t>
+          <t>2024.02.02 09:30-02.02 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>732</v>
+        <v>119</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -592,12 +594,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,40 +609,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华（取消）</t>
+          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>解放路15号 凤凰湖国际大酒店</t>
+          <t>滨江西路66号 万达广场</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.02 09:30-02.02 17:00</t>
+          <t>2024.02.03 14:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>119</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.33</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
         </is>
       </c>
     </row>
@@ -655,33 +655,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>吉水·only one游戏动漫节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 09:30-02.03 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
         </is>
       </c>
     </row>
@@ -696,33 +696,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>胜利北路208号 欧暇·地中海酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
         </is>
       </c>
     </row>
@@ -737,33 +737,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,38 +773,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>447</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -819,33 +819,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -860,33 +860,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>564</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -896,38 +896,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>556</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -942,33 +942,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>294</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -983,33 +983,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>289</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1019,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>363</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1079,19 +1079,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>351</v>
-      </c>
-      <c r="G16" t="n">
-        <v>50</v>
+        <v>112</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -1101,40 +1103,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>112</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="G17" t="n">
+        <v>50</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -1149,33 +1149,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>870</v>
+        <v>897</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
         <v>40</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="G33" t="n">
         <v>40</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1601</v>
+        <v>1608</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3499</v>
+        <v>3573</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2214,38 +2214,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -2260,33 +2260,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -2301,33 +2301,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="G46" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2337,36 +2337,77 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>南昌·原X穹X崩only</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>丰和北大道299号 新吉花园酒店</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>42</v>
+      </c>
+      <c r="G47" t="n">
+        <v>65</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>2024-03-30</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>10</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G48" t="n">
         <v>60</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -2501,7 +2542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2555,38 +2596,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>迎宾大道566号 荣耀国际酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.30 10:00-01.30 17:00</t>
+          <t>2024.02.01 10:00-02.01 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/8YmblqtV1706524591857.png</t>
         </is>
       </c>
     </row>
@@ -2596,38 +2637,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·第三届半夏动漫展（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣耀国际酒店</t>
+          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.02 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G3" t="n">
-        <v>45</v>
+        <v>732</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/8YmblqtV1706524591857.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
         </is>
       </c>
     </row>
@@ -2642,21 +2685,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>赣州·第三届半夏动漫展（取消）</t>
+          <t>高安·星语动漫嘉年华（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
+          <t>解放路15号 凤凰湖国际大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.02 10:00-02.04 17:00</t>
+          <t>2024.02.02 09:30-02.02 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>732</v>
+        <v>119</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2665,12 +2708,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
         </is>
       </c>
     </row>
@@ -2680,40 +2723,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华（取消）</t>
+          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>解放路15号 凤凰湖国际大酒店</t>
+          <t>滨江西路66号 万达广场</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.02 09:30-02.02 17:00</t>
+          <t>2024.02.03 14:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>119</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.33</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
         </is>
       </c>
     </row>
@@ -2728,33 +2769,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>吉水·only one游戏动漫节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 09:30-02.03 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
         </is>
       </c>
     </row>
@@ -2769,33 +2810,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>胜利北路208号 欧暇·地中海酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
         </is>
       </c>
     </row>
@@ -2810,33 +2851,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -2846,38 +2887,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>447</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -2892,33 +2933,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -2933,33 +2974,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>564</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2969,38 +3010,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>556</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -3015,33 +3056,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>294</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -3056,33 +3097,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>289</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -3092,38 +3133,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>363</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -3138,12 +3179,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3152,19 +3193,21 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>351</v>
-      </c>
-      <c r="G16" t="n">
-        <v>50</v>
+        <v>112</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -3174,40 +3217,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>112</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="G17" t="n">
+        <v>50</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -3222,33 +3263,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3318,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3318,7 +3359,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -3359,7 +3400,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3400,7 +3441,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>870</v>
+        <v>897</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -3441,7 +3482,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -3482,7 +3523,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -3523,7 +3564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -3564,7 +3605,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3607,7 +3648,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -3689,7 +3730,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
         <v>40</v>
@@ -3730,7 +3771,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
@@ -3771,7 +3812,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3812,7 +3853,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -3853,7 +3894,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="G33" t="n">
         <v>40</v>
@@ -3894,7 +3935,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1601</v>
+        <v>1608</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -3935,7 +3976,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -4058,7 +4099,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -4142,7 +4183,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3499</v>
+        <v>3573</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -4183,7 +4224,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -4224,7 +4265,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -4265,7 +4306,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -4287,38 +4328,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -4333,33 +4374,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -4374,33 +4415,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="G46" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -4410,36 +4451,77 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>南昌·原X穹X崩only</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>丰和北大道299号 新吉花园酒店</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>42</v>
+      </c>
+      <c r="G47" t="n">
+        <v>65</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>2024-03-30</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>10</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G48" t="n">
         <v>60</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
         <v>35</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
         <v>22.33</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>897</v>
+        <v>913</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G33" t="n">
         <v>40</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1608</v>
+        <v>1614</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3573</v>
+        <v>3610</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
         <v>35</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
         <v>22.33</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>897</v>
+        <v>913</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G33" t="n">
         <v>40</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1608</v>
+        <v>1614</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3573</v>
+        <v>3610</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
         <v>22.33</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
         <v>35</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
         <v>22.33</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>913</v>
+        <v>935</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G33" t="n">
         <v>40</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1614</v>
+        <v>1621</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3610</v>
+        <v>3651</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G44" t="n">
         <v>55</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
         <v>22.33</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
         <v>35</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
         <v>22.33</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>913</v>
+        <v>935</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" t="n">
         <v>40</v>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G33" t="n">
         <v>40</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1614</v>
+        <v>1621</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3610</v>
+        <v>3651</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G44" t="n">
         <v>55</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
         <v>22.33</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
         <v>35</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
         <v>22.33</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G29" t="n">
         <v>55</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G36" t="n">
         <v>30</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3651</v>
+        <v>3690</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
         <v>22.33</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G6" t="n">
         <v>35</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
         <v>35</v>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
         <v>22.33</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
         <v>35</v>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="G23" t="n">
         <v>45</v>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G29" t="n">
         <v>55</v>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G32" t="n">
         <v>55</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G36" t="n">
         <v>30</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3651</v>
+        <v>3690</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="G41" t="n">
         <v>45</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G42" t="n">
         <v>30</v>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·第三届半夏动漫展（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣耀国际酒店</t>
+          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.02 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G2" t="n">
-        <v>55</v>
+        <v>732</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/8YmblqtV1706524591857.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
         </is>
       </c>
     </row>
@@ -528,21 +530,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>赣州·第三届半夏动漫展（取消）</t>
+          <t>高安·星语动漫嘉年华（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
+          <t>解放路15号 凤凰湖国际大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.02 10:00-02.04 17:00</t>
+          <t>2024.02.02 09:30-02.02 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>732</v>
+        <v>119</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -551,12 +553,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,40 +568,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华（取消）</t>
+          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>解放路15号 凤凰湖国际大酒店</t>
+          <t>滨江西路66号 万达广场</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.02 09:30-02.02 17:00</t>
+          <t>2024.02.03 14:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>22.33</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
         </is>
       </c>
     </row>
@@ -614,33 +614,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>吉水·only one游戏动漫节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 09:30-02.03 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="G5" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
         </is>
       </c>
     </row>
@@ -655,33 +655,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>胜利北路208号 欧暇·地中海酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
         </is>
       </c>
     </row>
@@ -696,33 +696,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>467</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -732,38 +732,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>462</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -778,33 +778,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -819,33 +819,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>584</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,38 +855,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>577</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -901,33 +901,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>310</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -942,33 +942,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>302</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -978,38 +978,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1038,19 +1038,21 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>374</v>
-      </c>
-      <c r="G15" t="n">
-        <v>50</v>
+        <v>112</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -1060,40 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>112</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>97</v>
+      </c>
+      <c r="G16" t="n">
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -1108,33 +1108,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -1144,38 +1144,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1185,38 +1185,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -1231,33 +1231,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -1272,33 +1272,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>976</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -1313,33 +1313,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>947</v>
+        <v>1411</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -1354,33 +1354,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1402</v>
+        <v>307</v>
       </c>
       <c r="G23" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -1395,33 +1395,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -1436,33 +1436,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>330</v>
-      </c>
-      <c r="G25" t="n">
-        <v>50</v>
+        <v>184</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1472,40 +1474,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>184</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>77</v>
+      </c>
+      <c r="G26" t="n">
+        <v>45</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -1520,33 +1520,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="G27" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -1561,33 +1561,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="G28" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -1597,38 +1597,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="G29" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1643,33 +1643,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="G30" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1679,38 +1679,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1725,33 +1725,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="G32" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1766,33 +1766,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>275</v>
+        <v>1634</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1802,38 +1802,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1624</v>
+        <v>54</v>
       </c>
       <c r="G34" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1848,33 +1848,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1884,38 +1884,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G36" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1925,38 +1925,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>160</v>
+        <v>589</v>
       </c>
       <c r="G37" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1971,33 +1971,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>584</v>
-      </c>
-      <c r="G38" t="n">
-        <v>65</v>
+        <v>298</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -2007,40 +2009,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>299</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>3737</v>
+      </c>
+      <c r="G39" t="n">
+        <v>65</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -2055,33 +2055,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3690</v>
+        <v>435</v>
       </c>
       <c r="G40" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -2096,33 +2096,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>429</v>
+        <v>208</v>
       </c>
       <c r="G41" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -2132,38 +2132,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>203</v>
+        <v>923</v>
       </c>
       <c r="G42" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
         </is>
       </c>
     </row>
@@ -2173,38 +2173,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>912</v>
+        <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -2214,38 +2214,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="G44" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -2260,33 +2260,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2301,33 +2301,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -2337,77 +2337,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>10</v>
-      </c>
-      <c r="G48" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -2542,7 +2501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2596,38 +2555,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>抚州·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·第三届半夏动漫展（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣耀国际酒店</t>
+          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.01 10:00-02.01 17:00</t>
+          <t>2024.02.02 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G2" t="n">
-        <v>55</v>
+        <v>732</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80636</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/8YmblqtV1706524591857.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
         </is>
       </c>
     </row>
@@ -2642,21 +2603,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>赣州·第三届半夏动漫展（取消）</t>
+          <t>高安·星语动漫嘉年华（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
+          <t>解放路15号 凤凰湖国际大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.02 10:00-02.04 17:00</t>
+          <t>2024.02.02 09:30-02.02 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>732</v>
+        <v>119</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2665,12 +2626,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
         </is>
       </c>
     </row>
@@ -2680,40 +2641,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华（取消）</t>
+          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>解放路15号 凤凰湖国际大酒店</t>
+          <t>滨江西路66号 万达广场</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.02 09:30-02.02 17:00</t>
+          <t>2024.02.03 14:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>22.33</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
         </is>
       </c>
     </row>
@@ -2728,33 +2687,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>吉水·only one游戏动漫节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 09:30-02.03 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="G5" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
         </is>
       </c>
     </row>
@@ -2769,33 +2728,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>胜利北路208号 欧暇·地中海酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
         </is>
       </c>
     </row>
@@ -2810,33 +2769,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>467</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -2846,38 +2805,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>462</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -2892,33 +2851,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -2933,33 +2892,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>584</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2969,38 +2928,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>577</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -3015,33 +2974,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>310</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -3056,33 +3015,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>302</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -3092,38 +3051,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -3138,12 +3097,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3152,19 +3111,21 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>374</v>
-      </c>
-      <c r="G15" t="n">
-        <v>50</v>
+        <v>112</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -3174,40 +3135,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>112</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>97</v>
+      </c>
+      <c r="G16" t="n">
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -3222,33 +3181,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -3258,38 +3217,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -3299,38 +3258,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -3345,33 +3304,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -3386,33 +3345,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>976</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -3427,33 +3386,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>947</v>
+        <v>1411</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -3468,33 +3427,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1402</v>
+        <v>307</v>
       </c>
       <c r="G23" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -3509,33 +3468,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3550,33 +3509,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>330</v>
-      </c>
-      <c r="G25" t="n">
-        <v>50</v>
+        <v>184</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -3586,40 +3547,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>184</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>77</v>
+      </c>
+      <c r="G26" t="n">
+        <v>45</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -3634,33 +3593,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="G27" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -3675,33 +3634,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="G28" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -3711,38 +3670,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="G29" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -3757,33 +3716,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="G30" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -3793,38 +3752,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3839,33 +3798,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="G32" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3880,33 +3839,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>275</v>
+        <v>1634</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -3916,38 +3875,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1624</v>
+        <v>54</v>
       </c>
       <c r="G34" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -3962,33 +3921,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -3998,38 +3957,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G36" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -4039,38 +3998,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>160</v>
+        <v>589</v>
       </c>
       <c r="G37" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -4085,33 +4044,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>584</v>
-      </c>
-      <c r="G38" t="n">
-        <v>65</v>
+        <v>298</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4121,40 +4082,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>299</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>3737</v>
+      </c>
+      <c r="G39" t="n">
+        <v>65</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -4169,33 +4128,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3690</v>
+        <v>435</v>
       </c>
       <c r="G40" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -4210,33 +4169,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>429</v>
+        <v>208</v>
       </c>
       <c r="G41" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -4246,38 +4205,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>203</v>
+        <v>923</v>
       </c>
       <c r="G42" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
         </is>
       </c>
     </row>
@@ -4287,38 +4246,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>912</v>
+        <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -4328,38 +4287,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="G44" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -4374,33 +4333,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -4415,33 +4374,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -4451,77 +4410,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>10</v>
-      </c>
-      <c r="G48" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
         <v>35</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G14" t="n">
         <v>50</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
         <v>22.33</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
         <v>35</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>976</v>
+        <v>990</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="G22" t="n">
         <v>45</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G23" t="n">
         <v>50</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="n">
         <v>45</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G27" t="n">
         <v>48</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G29" t="n">
         <v>40</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G32" t="n">
         <v>40</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="G33" t="n">
         <v>50</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3737</v>
+        <v>3762</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G40" t="n">
         <v>45</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G41" t="n">
         <v>30</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G46" t="n">
         <v>65</v>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
         <v>35</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G14" t="n">
         <v>50</v>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
         <v>22.33</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
         <v>35</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>976</v>
+        <v>990</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="G22" t="n">
         <v>45</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G23" t="n">
         <v>50</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="n">
         <v>45</v>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G27" t="n">
         <v>48</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G29" t="n">
         <v>40</v>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G32" t="n">
         <v>40</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="G33" t="n">
         <v>50</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3737</v>
+        <v>3762</v>
       </c>
       <c r="G39" t="n">
         <v>65</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G40" t="n">
         <v>45</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G41" t="n">
         <v>30</v>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G46" t="n">
         <v>65</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,40 +525,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华（取消）</t>
+          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>解放路15号 凤凰湖国际大酒店</t>
+          <t>滨江西路66号 万达广场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.02 09:30-02.02 17:00</t>
+          <t>2024.02.03 14:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>119</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22.33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
         </is>
       </c>
     </row>
@@ -573,33 +571,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>吉水·only one游戏动漫节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 09:30-02.03 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="G4" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
         </is>
       </c>
     </row>
@@ -614,33 +612,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>胜利北路208号 欧暇·地中海酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
         </is>
       </c>
     </row>
@@ -655,33 +653,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>475</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>469</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -737,33 +735,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -778,33 +776,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>599</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>589</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -860,33 +858,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -901,33 +899,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>314</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -937,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>386</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -983,12 +981,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -997,19 +995,21 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>382</v>
-      </c>
-      <c r="G14" t="n">
-        <v>50</v>
+        <v>112</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -1019,40 +1019,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>106</v>
+      </c>
+      <c r="G15" t="n">
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -1067,33 +1065,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -1103,38 +1101,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1144,38 +1142,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -1190,33 +1188,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -1231,33 +1229,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>101</v>
+        <v>1013</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -1272,33 +1270,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>990</v>
+        <v>1422</v>
       </c>
       <c r="G21" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -1313,33 +1311,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1414</v>
+        <v>309</v>
       </c>
       <c r="G22" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -1354,33 +1352,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="G23" t="n">
         <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -1395,33 +1393,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>338</v>
-      </c>
-      <c r="G24" t="n">
-        <v>50</v>
+        <v>185</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1431,40 +1431,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>184</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>81</v>
+      </c>
+      <c r="G25" t="n">
+        <v>45</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -1479,33 +1477,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="G26" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -1520,33 +1518,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -1556,38 +1554,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="G28" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1602,33 +1600,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>89</v>
+        <v>235</v>
       </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1638,38 +1636,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1684,33 +1682,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="G31" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1725,33 +1723,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>277</v>
+        <v>1646</v>
       </c>
       <c r="G32" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1761,38 +1759,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1638</v>
+        <v>55</v>
       </c>
       <c r="G33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1807,33 +1805,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1843,38 +1841,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="G35" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1884,38 +1882,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>159</v>
+        <v>592</v>
       </c>
       <c r="G36" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1930,33 +1928,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>589</v>
-      </c>
-      <c r="G37" t="n">
-        <v>65</v>
+        <v>298</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1966,40 +1966,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>298</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>3790</v>
+      </c>
+      <c r="G38" t="n">
+        <v>65</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -2014,33 +2012,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3762</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G40" t="n">
         <v>45</v>
@@ -2110,7 +2108,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G41" t="n">
         <v>30</v>
@@ -2151,7 +2149,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>928</v>
+        <v>942</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -2163,7 +2161,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -2178,33 +2176,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G43" t="n">
         <v>55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -2214,38 +2212,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -2260,33 +2258,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -2301,33 +2299,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G46" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2337,36 +2335,77 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>南昌·原X穹X崩only</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>丰和北大道299号 新吉花园酒店</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>44</v>
+      </c>
+      <c r="G47" t="n">
+        <v>65</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>2024-03-30</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>10</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G48" t="n">
         <v>60</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -2501,7 +2540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2598,40 +2637,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>高安·星语动漫嘉年华（取消）</t>
+          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>解放路15号 凤凰湖国际大酒店</t>
+          <t>滨江西路66号 万达广场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.02 09:30-02.02 17:00</t>
+          <t>2024.02.03 14:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>119</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22.33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80316</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/9RuoGVYo1703757366286.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
         </is>
       </c>
     </row>
@@ -2646,33 +2683,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>吉水·only one游戏动漫节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 09:30-02.03 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="G4" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
         </is>
       </c>
     </row>
@@ -2687,33 +2724,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>胜利北路208号 欧暇·地中海酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
         </is>
       </c>
     </row>
@@ -2728,33 +2765,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>475</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -2764,38 +2801,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>469</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -2810,33 +2847,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -2851,33 +2888,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>599</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2887,38 +2924,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>589</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -2933,33 +2970,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -2974,33 +3011,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>314</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -3010,38 +3047,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>386</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3093,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3070,19 +3107,21 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>382</v>
-      </c>
-      <c r="G14" t="n">
-        <v>50</v>
+        <v>112</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -3092,40 +3131,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>106</v>
+      </c>
+      <c r="G15" t="n">
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -3140,33 +3177,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -3176,38 +3213,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -3217,38 +3254,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -3263,33 +3300,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -3304,33 +3341,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>101</v>
+        <v>1013</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -3345,33 +3382,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>990</v>
+        <v>1422</v>
       </c>
       <c r="G21" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -3386,33 +3423,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1414</v>
+        <v>309</v>
       </c>
       <c r="G22" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -3427,33 +3464,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="G23" t="n">
         <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3468,33 +3505,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>338</v>
-      </c>
-      <c r="G24" t="n">
-        <v>50</v>
+        <v>185</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -3504,40 +3543,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>184</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>81</v>
+      </c>
+      <c r="G25" t="n">
+        <v>45</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -3552,33 +3589,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="G26" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -3593,33 +3630,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -3629,38 +3666,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="G28" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -3675,33 +3712,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>89</v>
+        <v>235</v>
       </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -3711,38 +3748,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3757,33 +3794,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="G31" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3798,33 +3835,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>277</v>
+        <v>1646</v>
       </c>
       <c r="G32" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -3834,38 +3871,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1638</v>
+        <v>55</v>
       </c>
       <c r="G33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -3880,33 +3917,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -3916,38 +3953,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="G35" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3957,38 +3994,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>159</v>
+        <v>592</v>
       </c>
       <c r="G36" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -4003,33 +4040,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>589</v>
-      </c>
-      <c r="G37" t="n">
-        <v>65</v>
+        <v>298</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4039,40 +4078,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>298</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>3790</v>
+      </c>
+      <c r="G38" t="n">
+        <v>65</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -4087,33 +4124,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3762</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4179,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G40" t="n">
         <v>45</v>
@@ -4183,7 +4220,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G41" t="n">
         <v>30</v>
@@ -4224,7 +4261,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>928</v>
+        <v>942</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -4236,7 +4273,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/M8SHvWBS1702023166286.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4251,33 +4288,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G43" t="n">
         <v>55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -4287,38 +4324,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -4333,33 +4370,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -4374,33 +4411,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G46" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -4410,36 +4447,77 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>南昌·原X穹X崩only</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>丰和北大道299号 新吉花园酒店</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.23 17:00</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>44</v>
+      </c>
+      <c r="G47" t="n">
+        <v>65</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>2024-03-30</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>10</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G48" t="n">
         <v>60</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -667,10 +667,12 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>475</v>
-      </c>
-      <c r="G6" t="n">
-        <v>55</v>
+        <v>477</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -790,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -872,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G11" t="n">
         <v>45</v>
@@ -913,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -954,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -1079,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
         <v>22.33</v>
@@ -1120,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1202,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1243,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1013</v>
+        <v>1026</v>
       </c>
       <c r="G20" t="n">
         <v>55</v>
@@ -1284,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="G21" t="n">
         <v>45</v>
@@ -1325,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
@@ -1366,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G23" t="n">
         <v>50</v>
@@ -1450,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G25" t="n">
         <v>45</v>
@@ -1532,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
         <v>55</v>
@@ -1614,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1655,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G30" t="n">
         <v>55</v>
@@ -1696,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G31" t="n">
         <v>40</v>
@@ -1819,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -1860,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -1901,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G36" t="n">
         <v>65</v>
@@ -1942,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1985,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3790</v>
+        <v>3814</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -2026,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
         <v>10</v>
@@ -2067,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="G40" t="n">
         <v>45</v>
@@ -2108,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G41" t="n">
         <v>30</v>
@@ -2149,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>942</v>
+        <v>957</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -2190,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G43" t="n">
         <v>55</v>
@@ -2313,7 +2315,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -2656,7 +2658,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -2697,10 +2699,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2738,10 +2740,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2779,10 +2781,12 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>475</v>
-      </c>
-      <c r="G6" t="n">
-        <v>55</v>
+        <v>477</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2902,7 +2906,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -2984,7 +2988,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G11" t="n">
         <v>45</v>
@@ -3025,7 +3029,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -3066,7 +3070,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -3191,7 +3195,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
         <v>22.33</v>
@@ -3232,7 +3236,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3314,7 +3318,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3355,7 +3359,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1013</v>
+        <v>1026</v>
       </c>
       <c r="G20" t="n">
         <v>55</v>
@@ -3396,7 +3400,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="G21" t="n">
         <v>45</v>
@@ -3437,7 +3441,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
@@ -3478,7 +3482,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G23" t="n">
         <v>50</v>
@@ -3562,7 +3566,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G25" t="n">
         <v>45</v>
@@ -3644,7 +3648,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
         <v>55</v>
@@ -3726,7 +3730,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3767,7 +3771,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G30" t="n">
         <v>55</v>
@@ -3808,7 +3812,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G31" t="n">
         <v>40</v>
@@ -3931,7 +3935,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -3972,7 +3976,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G35" t="n">
         <v>40</v>
@@ -4013,7 +4017,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G36" t="n">
         <v>65</v>
@@ -4054,7 +4058,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4097,7 +4101,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3790</v>
+        <v>3814</v>
       </c>
       <c r="G38" t="n">
         <v>65</v>
@@ -4138,7 +4142,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
         <v>10</v>
@@ -4179,7 +4183,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="G40" t="n">
         <v>45</v>
@@ -4220,7 +4224,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G41" t="n">
         <v>30</v>
@@ -4261,7 +4265,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>942</v>
+        <v>957</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -4302,7 +4306,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G43" t="n">
         <v>55</v>
@@ -4425,7 +4429,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -530,33 +530,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
-      </c>
-      <c r="G3" t="n">
-        <v>22.33</v>
+        <v>479</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,38 +568,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +609,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,40 +650,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>477</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>616</v>
+      </c>
+      <c r="G6" t="n">
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,38 +691,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -732,38 +732,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>331</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -773,38 +773,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>603</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -814,38 +814,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
-      </c>
-      <c r="G10" t="n">
-        <v>58</v>
+        <v>395</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,38 +857,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>326</v>
-      </c>
-      <c r="G11" t="n">
-        <v>45</v>
+        <v>112</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -896,38 +900,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -937,38 +941,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>389</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -978,40 +982,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>112</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1021,38 +1023,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -1062,38 +1064,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="G16" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -1103,38 +1105,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>1054</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -1149,33 +1151,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>54</v>
+        <v>1433</v>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -1190,33 +1192,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>104</v>
+        <v>313</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -1231,33 +1233,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1026</v>
+        <v>349</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -1272,33 +1274,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1429</v>
-      </c>
-      <c r="G21" t="n">
-        <v>45</v>
+        <v>185</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1308,38 +1312,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>311</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -1349,38 +1353,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>344</v>
+        <v>157</v>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -1390,40 +1394,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>185</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="G24" t="n">
+        <v>55</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -1433,38 +1435,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G25" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1474,38 +1476,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>157</v>
+        <v>241</v>
       </c>
       <c r="G26" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1515,38 +1517,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>46</v>
+        <v>270</v>
       </c>
       <c r="G27" t="n">
         <v>55</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1556,38 +1558,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>89</v>
+        <v>292</v>
       </c>
       <c r="G28" t="n">
         <v>40</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1597,38 +1599,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>237</v>
+        <v>1654</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1638,38 +1640,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>268</v>
+        <v>58</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1679,38 +1681,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>286</v>
+        <v>104</v>
       </c>
       <c r="G31" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1720,38 +1722,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1646</v>
+        <v>161</v>
       </c>
       <c r="G32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1761,38 +1763,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>55</v>
+        <v>601</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1802,38 +1804,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>103</v>
-      </c>
-      <c r="G34" t="n">
-        <v>30</v>
+        <v>299</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1843,38 +1847,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>160</v>
+        <v>3847</v>
       </c>
       <c r="G35" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1884,38 +1888,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>594</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1925,40 +1929,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>299</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>446</v>
+      </c>
+      <c r="G37" t="n">
+        <v>45</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1973,33 +1975,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3814</v>
+        <v>221</v>
       </c>
       <c r="G38" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -2009,38 +2011,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>966</v>
       </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -2050,38 +2052,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>444</v>
+        <v>76</v>
       </c>
       <c r="G40" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -2091,38 +2093,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="G41" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -2132,38 +2134,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>957</v>
+        <v>20</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -2173,38 +2175,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="G43" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2214,38 +2216,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G44" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -2255,159 +2257,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>84</v>
-      </c>
-      <c r="G46" t="n">
-        <v>60</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G47" t="n">
-        <v>65</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>10</v>
-      </c>
-      <c r="G48" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -2542,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2615,7 +2494,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2644,33 +2523,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上饶·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>滨江西路66号 万达广场</t>
+          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 14:00-02.03 18:00</t>
+          <t>2024.02.03 10:00-02.04 20:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
-      </c>
-      <c r="G3" t="n">
-        <v>22.33</v>
+        <v>479</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81301</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/JDNFFJAM1706002602532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
         </is>
       </c>
     </row>
@@ -2680,38 +2561,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>吉水·only one游戏动漫节</t>
+          <t>宜丰·第六届浮光动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>龙华北大道万尚购物中心2期1楼 万尚购物中心(吉水店)</t>
+          <t>渊明北大道1号 宜丰大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 17:00</t>
+          <t>2024.02.04 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80403</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/vgJN9cJg1704781895960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
         </is>
       </c>
     </row>
@@ -2721,38 +2602,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新余·原神&amp;崩铁&amp;崩坏only</t>
+          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>胜利北路208号 欧暇·地中海酒店</t>
+          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.04 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80580</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BjtgGUbI1706525642100.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
         </is>
       </c>
     </row>
@@ -2762,40 +2643,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>477</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>616</v>
+      </c>
+      <c r="G6" t="n">
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2805,38 +2684,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -2846,38 +2725,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>331</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -2887,38 +2766,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>603</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -2928,38 +2807,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
-      </c>
-      <c r="G10" t="n">
-        <v>58</v>
+        <v>395</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -2969,38 +2850,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>326</v>
-      </c>
-      <c r="G11" t="n">
-        <v>45</v>
+        <v>112</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -3010,38 +2893,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -3051,38 +2934,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>389</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -3092,40 +2975,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>112</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -3135,38 +3016,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -3176,38 +3057,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="G16" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -3217,38 +3098,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>1054</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -3263,33 +3144,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>54</v>
+        <v>1433</v>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -3304,33 +3185,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>104</v>
+        <v>313</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -3345,33 +3226,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1026</v>
+        <v>349</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3386,33 +3267,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1429</v>
-      </c>
-      <c r="G21" t="n">
-        <v>45</v>
+        <v>185</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -3422,38 +3305,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>311</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -3463,38 +3346,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>344</v>
+        <v>157</v>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -3504,40 +3387,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>185</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="G24" t="n">
+        <v>55</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -3547,38 +3428,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G25" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -3588,38 +3469,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>157</v>
+        <v>241</v>
       </c>
       <c r="G26" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -3629,38 +3510,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>46</v>
+        <v>270</v>
       </c>
       <c r="G27" t="n">
         <v>55</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3670,38 +3551,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>89</v>
+        <v>292</v>
       </c>
       <c r="G28" t="n">
         <v>40</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3711,38 +3592,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>237</v>
+        <v>1654</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -3752,38 +3633,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>268</v>
+        <v>58</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -3793,38 +3674,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>286</v>
+        <v>104</v>
       </c>
       <c r="G31" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -3834,38 +3715,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1646</v>
+        <v>161</v>
       </c>
       <c r="G32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3875,38 +3756,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>55</v>
+        <v>601</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -3916,38 +3797,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>103</v>
-      </c>
-      <c r="G34" t="n">
-        <v>30</v>
+        <v>299</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -3957,38 +3840,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>160</v>
+        <v>3847</v>
       </c>
       <c r="G35" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -3998,38 +3881,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>594</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -4039,40 +3922,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>299</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>446</v>
+      </c>
+      <c r="G37" t="n">
+        <v>45</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -4087,33 +3968,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3814</v>
+        <v>221</v>
       </c>
       <c r="G38" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -4123,38 +4004,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>966</v>
       </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4164,38 +4045,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>444</v>
+        <v>76</v>
       </c>
       <c r="G40" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -4205,38 +4086,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="G41" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -4246,38 +4127,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>957</v>
+        <v>20</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -4287,38 +4168,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="G43" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -4328,38 +4209,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G44" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -4369,159 +4250,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>84</v>
-      </c>
-      <c r="G46" t="n">
-        <v>60</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G47" t="n">
-        <v>65</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>10</v>
-      </c>
-      <c r="G48" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
         <v>22.33</v>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="G18" t="n">
         <v>45</v>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G20" t="n">
         <v>50</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" t="n">
         <v>45</v>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G23" t="n">
         <v>48</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G27" t="n">
         <v>55</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G28" t="n">
         <v>40</v>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="G29" t="n">
         <v>50</v>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="G33" t="n">
         <v>65</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3847</v>
+        <v>3866</v>
       </c>
       <c r="G35" t="n">
         <v>65</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G37" t="n">
         <v>45</v>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G38" t="n">
         <v>30</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G40" t="n">
         <v>55</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
         <v>22.33</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="G18" t="n">
         <v>45</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G20" t="n">
         <v>50</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" t="n">
         <v>45</v>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G23" t="n">
         <v>48</v>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G27" t="n">
         <v>55</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G28" t="n">
         <v>40</v>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="G29" t="n">
         <v>50</v>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="G33" t="n">
         <v>65</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3847</v>
+        <v>3866</v>
       </c>
       <c r="G35" t="n">
         <v>65</v>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G37" t="n">
         <v>45</v>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G38" t="n">
         <v>30</v>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G40" t="n">
         <v>55</v>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赣州·第三届半夏动漫展（取消）</t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.02 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>735</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>626</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,26 +523,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>480</v>
+        <v>41</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -553,12 +551,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -568,38 +566,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>346</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -609,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -650,38 +648,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>622</v>
-      </c>
-      <c r="G6" t="n">
-        <v>55</v>
+        <v>404</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,38 +691,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
-      </c>
-      <c r="G7" t="n">
-        <v>58</v>
+        <v>112</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -732,38 +734,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>336</v>
+        <v>117</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,38 +775,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>22.33</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,40 +816,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>399</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -857,40 +857,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>112</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -900,38 +898,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -941,38 +939,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>1083</v>
       </c>
       <c r="G13" t="n">
-        <v>22.33</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -982,38 +980,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>1446</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -1028,33 +1026,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>317</v>
       </c>
       <c r="G15" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -1069,33 +1067,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>109</v>
+        <v>355</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -1110,33 +1108,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1065</v>
-      </c>
-      <c r="G17" t="n">
-        <v>55</v>
+        <v>183</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1146,38 +1146,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1432</v>
+        <v>92</v>
       </c>
       <c r="G18" t="n">
         <v>45</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -1187,38 +1187,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>315</v>
+        <v>158</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -1228,38 +1228,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>351</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,40 +1269,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>184</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>93</v>
+      </c>
+      <c r="G21" t="n">
+        <v>40</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1312,38 +1310,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>88</v>
+        <v>249</v>
       </c>
       <c r="G22" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1353,38 +1351,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>158</v>
+        <v>274</v>
       </c>
       <c r="G23" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1394,38 +1392,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="G24" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1435,38 +1433,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>92</v>
+        <v>1663</v>
       </c>
       <c r="G25" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1476,38 +1474,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>245</v>
+        <v>59</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1517,38 +1515,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="G27" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1558,38 +1556,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>293</v>
+        <v>164</v>
       </c>
       <c r="G28" t="n">
         <v>40</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1599,38 +1597,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1658</v>
+        <v>619</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1640,38 +1638,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>58</v>
-      </c>
-      <c r="G30" t="n">
-        <v>40</v>
+        <v>299</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1681,38 +1681,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>104</v>
+        <v>3898</v>
       </c>
       <c r="G31" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1722,38 +1722,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>161</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1763,38 +1763,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>605</v>
+        <v>454</v>
       </c>
       <c r="G33" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1804,40 +1804,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>300</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>224</v>
+      </c>
+      <c r="G34" t="n">
+        <v>30</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -1847,38 +1845,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3866</v>
+        <v>986</v>
       </c>
       <c r="G35" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1888,38 +1886,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1929,38 +1927,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>449</v>
+        <v>44</v>
       </c>
       <c r="G37" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1970,38 +1968,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="G38" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -2011,38 +2009,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>975</v>
+        <v>88</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2052,38 +2050,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G40" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -2093,200 +2091,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>上饶·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>五三东大道42号 回禾酒店</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>20</v>
-      </c>
-      <c r="G42" t="n">
-        <v>60</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>86</v>
-      </c>
-      <c r="G43" t="n">
-        <v>60</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>44</v>
-      </c>
-      <c r="G44" t="n">
-        <v>65</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>10</v>
-      </c>
-      <c r="G45" t="n">
-        <v>60</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -2421,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2475,40 +2309,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赣州·第三届半夏动漫展（取消）</t>
+          <t>赣州·ODK动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>105国道东100米赣州毅德城国际会展中心 赣州毅德城国际会展中心</t>
+          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.02 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:00-02.05 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>735</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>626</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eMehCxbh1702972507887.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2518,26 +2350,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">江西·起航·未来2024动漫展 </t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>永丰南大道1号永利国际大酒店 永利酒店</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 20:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>480</v>
+        <v>41</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2546,12 +2378,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79917</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/8kudlPuE1702901121965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -2561,38 +2393,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>宜丰·第六届浮光动漫游戏展</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>渊明北大道1号 宜丰大酒店</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 09:00-02.04 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>346</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81154</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/MyQjWch61705658763377.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -2602,38 +2434,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>宜春·原神&amp;崩铁&amp;崩坏only</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>向阳路万载县幼儿园东南侧约60米 禧莱国际大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 17:00</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81209</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SiAXR6ID1705906134087.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -2643,38 +2475,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>622</v>
-      </c>
-      <c r="G6" t="n">
-        <v>55</v>
+        <v>404</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -2684,38 +2518,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
-      </c>
-      <c r="G7" t="n">
-        <v>58</v>
+        <v>112</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -2725,38 +2561,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>336</v>
+        <v>117</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -2766,38 +2602,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>22.33</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -2807,40 +2643,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>399</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -2850,40 +2684,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>112</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -2893,38 +2725,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -2934,38 +2766,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>1083</v>
       </c>
       <c r="G13" t="n">
-        <v>22.33</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -2975,38 +2807,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>1446</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -3021,33 +2853,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>317</v>
       </c>
       <c r="G15" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -3062,33 +2894,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>109</v>
+        <v>355</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3103,33 +2935,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1065</v>
-      </c>
-      <c r="G17" t="n">
-        <v>55</v>
+        <v>183</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -3139,38 +2973,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1432</v>
+        <v>92</v>
       </c>
       <c r="G18" t="n">
         <v>45</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -3180,38 +3014,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>315</v>
+        <v>158</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -3221,38 +3055,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>351</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -3262,40 +3096,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>184</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>93</v>
+      </c>
+      <c r="G21" t="n">
+        <v>40</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -3305,38 +3137,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>88</v>
+        <v>249</v>
       </c>
       <c r="G22" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -3346,38 +3178,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>158</v>
+        <v>274</v>
       </c>
       <c r="G23" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3387,38 +3219,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="G24" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3428,38 +3260,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>92</v>
+        <v>1663</v>
       </c>
       <c r="G25" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -3469,38 +3301,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>245</v>
+        <v>59</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -3510,38 +3342,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="G27" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -3551,38 +3383,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>293</v>
+        <v>164</v>
       </c>
       <c r="G28" t="n">
         <v>40</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3592,38 +3424,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1658</v>
+        <v>619</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -3633,38 +3465,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>58</v>
-      </c>
-      <c r="G30" t="n">
-        <v>40</v>
+        <v>299</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -3674,38 +3508,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>104</v>
+        <v>3898</v>
       </c>
       <c r="G31" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -3715,38 +3549,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>161</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -3756,38 +3590,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>605</v>
+        <v>454</v>
       </c>
       <c r="G33" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -3797,40 +3631,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>300</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>224</v>
+      </c>
+      <c r="G34" t="n">
+        <v>30</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -3840,38 +3672,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3866</v>
+        <v>986</v>
       </c>
       <c r="G35" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -3881,38 +3713,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -3922,38 +3754,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>449</v>
+        <v>44</v>
       </c>
       <c r="G37" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -3963,38 +3795,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="G38" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -4004,38 +3836,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>975</v>
+        <v>88</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -4045,38 +3877,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G40" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -4086,200 +3918,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>上饶·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>五三东大道42号 回禾酒店</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>20</v>
-      </c>
-      <c r="G42" t="n">
-        <v>60</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>86</v>
-      </c>
-      <c r="G43" t="n">
-        <v>60</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>44</v>
-      </c>
-      <c r="G44" t="n">
-        <v>65</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>10</v>
-      </c>
-      <c r="G45" t="n">
-        <v>60</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
         <v>35</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1083</v>
+        <v>1101</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1446</v>
+        <v>1453</v>
       </c>
       <c r="G14" t="n">
         <v>45</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="n">
         <v>45</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
         <v>55</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G21" t="n">
         <v>40</v>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G24" t="n">
         <v>40</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1663</v>
+        <v>1670</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
         <v>40</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3898</v>
+        <v>3928</v>
       </c>
       <c r="G31" t="n">
         <v>65</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G33" t="n">
         <v>45</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
         <v>35</v>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1083</v>
+        <v>1101</v>
       </c>
       <c r="G13" t="n">
         <v>55</v>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1446</v>
+        <v>1453</v>
       </c>
       <c r="G14" t="n">
         <v>45</v>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="n">
         <v>45</v>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
         <v>55</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G21" t="n">
         <v>40</v>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G24" t="n">
         <v>40</v>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1663</v>
+        <v>1670</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
         <v>40</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3898</v>
+        <v>3928</v>
       </c>
       <c r="G31" t="n">
         <v>65</v>
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
         <v>10</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G33" t="n">
         <v>45</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -482,38 +482,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>627</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
+        <v>44</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -528,35 +530,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>368</v>
+      </c>
+      <c r="G3" t="n">
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -571,33 +571,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -607,38 +607,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
-      </c>
-      <c r="G5" t="n">
-        <v>55</v>
+        <v>410</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -653,12 +655,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -667,21 +669,21 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>410</v>
+        <v>114</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,40 +693,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>113</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>120</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -739,33 +739,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,38 +775,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -816,38 +816,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -862,33 +862,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -903,33 +903,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>114</v>
+        <v>1130</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -944,33 +944,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1101</v>
+        <v>1462</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -985,33 +985,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1453</v>
+        <v>323</v>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -1026,33 +1026,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -1067,33 +1067,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>357</v>
-      </c>
-      <c r="G16" t="n">
-        <v>50</v>
+        <v>183</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1103,40 +1105,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>183</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>97</v>
+      </c>
+      <c r="G17" t="n">
+        <v>45</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -1151,33 +1151,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="G18" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -1192,33 +1192,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="G19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -1228,38 +1228,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1274,33 +1274,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>95</v>
+        <v>255</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1310,38 +1310,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1356,33 +1356,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1397,33 +1397,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>301</v>
+        <v>1676</v>
       </c>
       <c r="G24" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1433,38 +1433,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1670</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1479,33 +1479,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1515,38 +1515,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1556,38 +1556,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>164</v>
+        <v>631</v>
       </c>
       <c r="G28" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1602,33 +1602,35 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>626</v>
-      </c>
-      <c r="G29" t="n">
-        <v>65</v>
+        <v>302</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1638,40 +1640,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>300</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>59</v>
+      </c>
+      <c r="G30" t="n">
+        <v>238</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3928</v>
+        <v>3961</v>
       </c>
       <c r="G31" t="n">
         <v>65</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G33" t="n">
         <v>45</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>994</v>
+        <v>1008</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -2309,38 +2309,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赣州·ODK动漫游戏嘉年华</t>
+          <t>宜春·ACG.mini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>赞贤路与长征大道交叉口东南200米赣州市少林功夫表演团附近 赣州市体育中心-体育馆</t>
+          <t>中山中路18号 步步高</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.05 17:00</t>
+          <t>2024.02.06 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>627</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
+        <v>44</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79968</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/7Dj98f0e1702973631185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
         </is>
       </c>
     </row>
@@ -2355,35 +2357,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>萍乡·FLower·“冬”</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.06 09:20-02.06 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>368</v>
+      </c>
+      <c r="G3" t="n">
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
         </is>
       </c>
     </row>
@@ -2398,33 +2398,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.06 10:00-02.06 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
         </is>
       </c>
     </row>
@@ -2434,38 +2434,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
-      </c>
-      <c r="G5" t="n">
-        <v>55</v>
+        <v>410</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2482,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2494,21 +2496,21 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>410</v>
+        <v>114</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -2518,40 +2520,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>113</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>120</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -2566,33 +2566,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>22.33</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -2602,38 +2602,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -2643,38 +2643,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -2689,33 +2689,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -2730,33 +2730,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>114</v>
+        <v>1130</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -2771,33 +2771,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1101</v>
+        <v>1462</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -2812,33 +2812,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1453</v>
+        <v>323</v>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -2853,33 +2853,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2894,33 +2894,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>357</v>
-      </c>
-      <c r="G16" t="n">
-        <v>50</v>
+        <v>183</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2930,40 +2932,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>183</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>97</v>
+      </c>
+      <c r="G17" t="n">
+        <v>45</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -2978,33 +2978,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="G18" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -3019,33 +3019,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="G19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -3055,38 +3055,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -3101,33 +3101,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>95</v>
+        <v>255</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -3137,38 +3137,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3183,33 +3183,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3224,33 +3224,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>301</v>
+        <v>1676</v>
       </c>
       <c r="G24" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -3260,38 +3260,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1670</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -3306,33 +3306,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -3342,38 +3342,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3383,38 +3383,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>164</v>
+        <v>631</v>
       </c>
       <c r="G28" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -3429,33 +3429,35 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>626</v>
-      </c>
-      <c r="G29" t="n">
-        <v>65</v>
+        <v>302</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -3465,40 +3467,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>300</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>59</v>
+      </c>
+      <c r="G30" t="n">
+        <v>238</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3928</v>
+        <v>3961</v>
       </c>
       <c r="G31" t="n">
         <v>65</v>
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
         <v>10</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G33" t="n">
         <v>45</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>994</v>
+        <v>1008</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G40" t="n">
         <v>65</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
         <v>22.33</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1130</v>
+        <v>1139</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G14" t="n">
         <v>50</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
         <v>45</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G23" t="n">
         <v>40</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G27" t="n">
         <v>40</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G28" t="n">
         <v>65</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="G30" t="n">
         <v>238</v>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3961</v>
+        <v>3977</v>
       </c>
       <c r="G31" t="n">
         <v>65</v>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="G33" t="n">
         <v>45</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
         <v>22.33</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1130</v>
+        <v>1139</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G14" t="n">
         <v>50</v>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
         <v>45</v>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G23" t="n">
         <v>40</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G27" t="n">
         <v>40</v>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G28" t="n">
         <v>65</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="G30" t="n">
         <v>238</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3961</v>
+        <v>3977</v>
       </c>
       <c r="G31" t="n">
         <v>65</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="G33" t="n">
         <v>45</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G34" t="n">
         <v>30</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,38 +525,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>376</v>
-      </c>
-      <c r="G3" t="n">
-        <v>50</v>
+        <v>413</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,38 +568,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G4" t="n">
-        <v>65</v>
+        <v>114</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,40 +611,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>411</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>124</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -650,40 +652,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22.33</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -693,38 +693,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -734,38 +734,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="G8" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,38 +775,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -821,33 +821,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>1165</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -862,33 +862,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>117</v>
+        <v>1476</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -903,33 +903,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1139</v>
+        <v>327</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -944,33 +944,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1466</v>
+        <v>363</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -985,33 +985,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>324</v>
-      </c>
-      <c r="G14" t="n">
-        <v>50</v>
+        <v>183</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1021,38 +1023,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>361</v>
+        <v>114</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -1062,40 +1064,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>183</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>160</v>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -1146,38 +1146,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="G18" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1187,38 +1187,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>56</v>
+        <v>259</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1228,38 +1228,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>98</v>
+        <v>281</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,38 +1269,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,33 +1315,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>280</v>
+        <v>1686</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1351,38 +1351,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>303</v>
+        <v>62</v>
       </c>
       <c r="G23" t="n">
         <v>40</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1392,38 +1392,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1679</v>
+        <v>104</v>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1433,38 +1433,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1474,38 +1474,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>104</v>
+        <v>638</v>
       </c>
       <c r="G26" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1515,38 +1515,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>165</v>
-      </c>
-      <c r="G27" t="n">
-        <v>40</v>
+        <v>302</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1556,38 +1558,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>633</v>
+        <v>169</v>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>238</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1597,40 +1599,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>302</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4013</v>
+      </c>
+      <c r="G29" t="n">
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1645,33 +1645,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>238</v>
+        <v>10</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1686,33 +1686,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3977</v>
+        <v>472</v>
       </c>
       <c r="G31" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1727,33 +1727,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>243</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -1763,38 +1763,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>465</v>
+        <v>1032</v>
       </c>
       <c r="G33" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1804,38 +1804,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>239</v>
+        <v>117</v>
       </c>
       <c r="G34" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1845,38 +1845,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1016</v>
+        <v>46</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1891,33 +1891,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="G36" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1927,38 +1927,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1973,33 +1973,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2014,33 +2014,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="G39" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -2050,77 +2050,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="G40" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>12</v>
-      </c>
-      <c r="G41" t="n">
-        <v>60</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -2255,7 +2214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2352,38 +2311,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>萍乡·FLower·“冬”</t>
+          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>凤凰街迎宾路18号 鸿凯大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.06 09:20-02.06 17:30</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>376</v>
-      </c>
-      <c r="G3" t="n">
-        <v>50</v>
+        <v>413</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79765</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1T4ZYb311704781450018.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
         </is>
       </c>
     </row>
@@ -2393,38 +2354,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>萍乡·原神&amp;崩铁&amp;崩坏only</t>
+          <t>九江·原X星X蔚蓝ONLY（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>公园南路168号(近工行城北分理处) 梅生嘉华酒店</t>
+          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.06 17:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G4" t="n">
-        <v>65</v>
+        <v>114</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80987</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pUW0TeEo1705547140191.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
         </is>
       </c>
     </row>
@@ -2434,40 +2397,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>411</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>124</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -2477,40 +2438,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22.33</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -2520,38 +2479,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -2561,38 +2520,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="G8" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -2602,38 +2561,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -2648,33 +2607,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>1165</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -2689,33 +2648,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>117</v>
+        <v>1476</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -2730,33 +2689,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1139</v>
+        <v>327</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -2771,33 +2730,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1466</v>
+        <v>363</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2812,33 +2771,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>324</v>
-      </c>
-      <c r="G14" t="n">
-        <v>50</v>
+        <v>183</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2848,38 +2809,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>361</v>
+        <v>114</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -2889,40 +2850,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>183</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>160</v>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2896,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2951,19 +2910,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -2973,38 +2932,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="G18" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -3014,38 +2973,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>56</v>
+        <v>259</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -3055,38 +3014,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>98</v>
+        <v>281</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3096,38 +3055,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3142,33 +3101,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>280</v>
+        <v>1686</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -3178,38 +3137,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>303</v>
+        <v>62</v>
       </c>
       <c r="G23" t="n">
         <v>40</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -3219,38 +3178,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1679</v>
+        <v>104</v>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -3260,38 +3219,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3301,38 +3260,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>104</v>
+        <v>638</v>
       </c>
       <c r="G26" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -3342,38 +3301,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>165</v>
-      </c>
-      <c r="G27" t="n">
-        <v>40</v>
+        <v>302</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -3383,38 +3344,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>633</v>
+        <v>169</v>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>238</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -3424,40 +3385,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>302</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4013</v>
+      </c>
+      <c r="G29" t="n">
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -3472,33 +3431,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>238</v>
+        <v>10</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -3513,33 +3472,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3977</v>
+        <v>472</v>
       </c>
       <c r="G31" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -3554,33 +3513,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>243</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
         </is>
       </c>
     </row>
@@ -3590,38 +3549,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>465</v>
+        <v>1032</v>
       </c>
       <c r="G33" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -3631,38 +3590,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>239</v>
+        <v>117</v>
       </c>
       <c r="G34" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -3672,38 +3631,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1016</v>
+        <v>46</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -3718,33 +3677,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="G36" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -3754,38 +3713,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -3800,33 +3759,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -3841,33 +3800,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="G39" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -3877,77 +3836,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="G40" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>12</v>
-      </c>
-      <c r="G41" t="n">
-        <v>60</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -544,11 +544,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G5" t="n">
         <v>50</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
         <v>22.33</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
         <v>35</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="G11" t="n">
         <v>45</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G15" t="n">
         <v>45</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G20" t="n">
         <v>55</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G21" t="n">
         <v>40</v>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1686</v>
+        <v>1692</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="G28" t="n">
         <v>238</v>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4013</v>
+        <v>4035</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G31" t="n">
         <v>45</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G32" t="n">
         <v>30</v>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -2330,11 +2330,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G5" t="n">
         <v>50</v>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
         <v>22.33</v>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
         <v>35</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="G11" t="n">
         <v>45</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G15" t="n">
         <v>45</v>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G20" t="n">
         <v>55</v>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G21" t="n">
         <v>40</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1686</v>
+        <v>1692</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G25" t="n">
         <v>40</v>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="G28" t="n">
         <v>238</v>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4013</v>
+        <v>4035</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G31" t="n">
         <v>45</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G32" t="n">
         <v>30</v>
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>130</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,40 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>414</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22.33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -568,40 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>114</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>59</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -611,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -652,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="G6" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -693,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>1193</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -739,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>1493</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -780,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>119</v>
+        <v>331</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -821,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1173</v>
+        <v>370</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -862,33 +856,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1478</v>
-      </c>
-      <c r="G11" t="n">
-        <v>45</v>
+        <v>183</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -898,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>328</v>
+        <v>130</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -939,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>365</v>
+        <v>161</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -980,40 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>183</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -1023,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="G15" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1064,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>160</v>
+        <v>265</v>
       </c>
       <c r="G16" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1105,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>288</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1146,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>314</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1187,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>261</v>
+        <v>1697</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1228,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>283</v>
+        <v>63</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1269,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1310,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1692</v>
+        <v>170</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1351,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>62</v>
+        <v>643</v>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1392,38 +1386,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>104</v>
-      </c>
-      <c r="G24" t="n">
-        <v>30</v>
+        <v>303</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1433,38 +1429,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>168</v>
-      </c>
-      <c r="G25" t="n">
-        <v>40</v>
+        <v>329</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1474,38 +1472,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>639</v>
+        <v>4069</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1515,40 +1513,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>303</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1563,33 +1559,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>212</v>
+        <v>475</v>
       </c>
       <c r="G28" t="n">
-        <v>238</v>
+        <v>45</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1604,33 +1600,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4035</v>
+        <v>251</v>
       </c>
       <c r="G29" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1640,38 +1636,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>1055</v>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1681,38 +1677,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>473</v>
+        <v>126</v>
       </c>
       <c r="G31" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1722,38 +1718,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>246</v>
+        <v>46</v>
       </c>
       <c r="G32" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1763,38 +1759,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1041</v>
+        <v>386</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1804,38 +1800,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="G34" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1845,38 +1841,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="G35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1886,38 +1882,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>282</v>
+        <v>46</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1927,159 +1923,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>154</v>
-      </c>
-      <c r="G38" t="n">
-        <v>60</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>46</v>
-      </c>
-      <c r="G39" t="n">
-        <v>65</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>12</v>
-      </c>
-      <c r="G40" t="n">
-        <v>60</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -2214,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,40 +2141,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>宜春·ACG.mini动漫游戏嘉年华</t>
+          <t>抚州·临次元06·新春国漫嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中山中路18号 步步高</t>
+          <t>迎宾大道566号 荣誉国际酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.06 10:00-02.07 17:00</t>
+          <t>2024.02.12 10:00-02.12 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>130</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81312</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/vW4KVPya1706006644306.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
         </is>
       </c>
     </row>
@@ -2311,40 +2182,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上饶·第十四届IX Group国风嘉年华-新年专场</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>414</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22.33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79912</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TcrwVL681702894421111.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -2354,40 +2223,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>九江·原X星X蔚蓝ONLY（取消）</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>十里大道202号（十里大道与地质路交汇处） 山水国际大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>114</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>59</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79733</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/rA0uINs51702454906179.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -2397,38 +2264,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -2438,38 +2305,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="G6" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -2479,38 +2346,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>1193</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -2525,33 +2392,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>1493</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -2566,33 +2433,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>119</v>
+        <v>331</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -2607,33 +2474,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1173</v>
+        <v>370</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2648,33 +2515,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1478</v>
-      </c>
-      <c r="G11" t="n">
-        <v>45</v>
+        <v>183</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2684,38 +2553,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>328</v>
+        <v>130</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -2725,38 +2594,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>365</v>
+        <v>161</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -2766,40 +2635,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>183</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -2809,38 +2676,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="G15" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -2850,38 +2717,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>160</v>
+        <v>265</v>
       </c>
       <c r="G16" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -2891,38 +2758,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>288</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -2932,38 +2799,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>314</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -2973,38 +2840,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>261</v>
+        <v>1697</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -3014,38 +2881,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>283</v>
+        <v>63</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -3055,38 +2922,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -3096,38 +2963,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1692</v>
+        <v>170</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3137,38 +3004,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>62</v>
+        <v>643</v>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -3178,38 +3045,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>104</v>
-      </c>
-      <c r="G24" t="n">
-        <v>30</v>
+        <v>303</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -3219,38 +3088,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>168</v>
-      </c>
-      <c r="G25" t="n">
-        <v>40</v>
+        <v>329</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -3260,38 +3131,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>639</v>
+        <v>4069</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -3301,40 +3172,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>303</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -3349,33 +3218,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>212</v>
+        <v>475</v>
       </c>
       <c r="G28" t="n">
-        <v>238</v>
+        <v>45</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -3390,33 +3259,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4035</v>
+        <v>251</v>
       </c>
       <c r="G29" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -3426,38 +3295,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>1055</v>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -3467,38 +3336,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>473</v>
+        <v>126</v>
       </c>
       <c r="G31" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -3508,38 +3377,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>246</v>
+        <v>46</v>
       </c>
       <c r="G32" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/XnQn6FCd1706007846463.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -3549,38 +3418,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1041</v>
+        <v>386</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -3590,38 +3459,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="G34" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -3631,38 +3500,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="G35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -3672,38 +3541,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>282</v>
+        <v>46</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -3713,159 +3582,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>154</v>
-      </c>
-      <c r="G38" t="n">
-        <v>60</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>46</v>
-      </c>
-      <c r="G39" t="n">
-        <v>65</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>12</v>
-      </c>
-      <c r="G40" t="n">
-        <v>60</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1193</v>
+        <v>1204</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1697</v>
+        <v>1702</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G21" t="n">
         <v>30</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4069</v>
+        <v>4091</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G28" t="n">
         <v>45</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G29" t="n">
         <v>30</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G36" t="n">
         <v>65</v>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1193</v>
+        <v>1204</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1697</v>
+        <v>1702</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G21" t="n">
         <v>30</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4069</v>
+        <v>4091</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G28" t="n">
         <v>45</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G29" t="n">
         <v>30</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G36" t="n">
         <v>65</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1204</v>
+        <v>1222</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1497</v>
+        <v>1509</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4091</v>
+        <v>4113</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G29" t="n">
         <v>30</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G36" t="n">
         <v>65</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1204</v>
+        <v>1222</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1497</v>
+        <v>1509</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4091</v>
+        <v>4113</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G29" t="n">
         <v>30</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G36" t="n">
         <v>65</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1706</v>
+        <v>1715</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4113</v>
+        <v>4123</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G29" t="n">
         <v>30</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1706</v>
+        <v>1715</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4113</v>
+        <v>4123</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G29" t="n">
         <v>30</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1228</v>
+        <v>1245</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1515</v>
+        <v>1529</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1715</v>
+        <v>1722</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4123</v>
+        <v>4144</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
         <v>10</v>
@@ -1559,33 +1559,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>476</v>
+        <v>263</v>
       </c>
       <c r="G28" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1595,38 +1595,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>257</v>
+        <v>1080</v>
       </c>
       <c r="G29" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1636,38 +1636,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1074</v>
+        <v>481</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1682,33 +1682,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1723,33 +1723,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>46</v>
+        <v>512</v>
       </c>
       <c r="G32" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1759,38 +1759,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>495</v>
+        <v>22</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1805,33 +1805,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>22</v>
+        <v>232</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1846,33 +1846,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>225</v>
+        <v>48</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1882,38 +1882,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="G36" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1228</v>
+        <v>1245</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1515</v>
+        <v>1529</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1715</v>
+        <v>1722</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4123</v>
+        <v>4144</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
         <v>10</v>
@@ -3218,33 +3218,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>476</v>
+        <v>263</v>
       </c>
       <c r="G28" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -3254,38 +3254,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>257</v>
+        <v>1080</v>
       </c>
       <c r="G29" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -3295,38 +3295,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1074</v>
+        <v>481</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -3341,33 +3341,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -3382,33 +3382,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>46</v>
+        <v>512</v>
       </c>
       <c r="G32" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -3418,38 +3418,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>495</v>
+        <v>22</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -3464,33 +3464,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>22</v>
+        <v>232</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -3505,33 +3505,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>225</v>
+        <v>48</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -3541,38 +3541,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="G36" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1245</v>
+        <v>1254</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1722</v>
+        <v>1728</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4144</v>
+        <v>4162</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1245</v>
+        <v>1254</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1722</v>
+        <v>1728</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4144</v>
+        <v>4162</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1254</v>
+        <v>1273</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1728</v>
+        <v>1737</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4162</v>
+        <v>4194</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1254</v>
+        <v>1273</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1728</v>
+        <v>1737</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4162</v>
+        <v>4194</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1273</v>
+        <v>1285</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1737</v>
+        <v>1744</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G21" t="n">
         <v>30</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4194</v>
+        <v>4211</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1273</v>
+        <v>1285</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1737</v>
+        <v>1744</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G21" t="n">
         <v>30</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4194</v>
+        <v>4211</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
         <v>10</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1285</v>
+        <v>1307</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1543</v>
+        <v>1554</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1744</v>
+        <v>1755</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>暂时售罄</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4211</v>
+        <v>4225</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G2" t="n">
         <v>50</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
         <v>22.33</v>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1285</v>
+        <v>1307</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1543</v>
+        <v>1554</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1744</v>
+        <v>1755</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>暂时售罄</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4211</v>
+        <v>4225</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
         <v>10</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1307</v>
+        <v>1319</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1755</v>
+        <v>1763</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>暂时售罄</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4225</v>
+        <v>4245</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G35" t="n">
         <v>65</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1307</v>
+        <v>1319</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" t="n">
         <v>40</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G18" t="n">
         <v>40</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1755</v>
+        <v>1763</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G20" t="n">
         <v>40</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>暂时售罄</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4225</v>
+        <v>4245</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G30" t="n">
         <v>45</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G35" t="n">
         <v>65</v>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,33 +487,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>22.33</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,33 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>136</v>
+        <v>1342</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1319</v>
+        <v>1576</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1562</v>
+        <v>346</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>343</v>
+        <v>443</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,33 +815,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>431</v>
-      </c>
-      <c r="G10" t="n">
-        <v>50</v>
+        <v>182</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,40 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>182</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>177</v>
+      </c>
+      <c r="G11" t="n">
+        <v>45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -899,33 +899,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -940,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1022,33 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>285</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1104,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,33 +1145,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>331</v>
+        <v>1771</v>
       </c>
       <c r="G18" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1763</v>
+        <v>74</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1227,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>179</v>
+        <v>697</v>
       </c>
       <c r="G22" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,33 +1350,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>686</v>
-      </c>
-      <c r="G23" t="n">
-        <v>65</v>
+        <v>304</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,40 +1388,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>304</v>
+        <v>347</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1436,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1444,25 +1446,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>345</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4279</v>
+      </c>
+      <c r="G25" t="n">
+        <v>65</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1477,33 +1477,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4245</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1518,33 +1518,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>292</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1554,38 +1554,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>286</v>
+        <v>1125</v>
       </c>
       <c r="G28" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1595,38 +1595,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1113</v>
+        <v>495</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1636,38 +1636,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>495</v>
+        <v>46</v>
       </c>
       <c r="G30" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1682,33 +1682,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>46</v>
+        <v>635</v>
       </c>
       <c r="G31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1718,38 +1718,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>614</v>
+        <v>24</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1764,33 +1764,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>23</v>
+        <v>326</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1805,33 +1805,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>310</v>
+        <v>50</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1841,38 +1841,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="G35" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1887,72 +1887,31 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="G36" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>14</v>
-      </c>
-      <c r="G37" t="n">
-        <v>60</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -2087,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2146,33 +2105,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>抚州·临次元06·新春国漫嘉年华</t>
+          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>迎宾大道566号 荣誉国际酒店</t>
+          <t>金岭东大道新都汇西侧约100米 万达广场</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.12 10:00-02.12 17:00</t>
+          <t>2024.02.12 14:00-02.13 19:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>22.33</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81110</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/pyOSrr2t1705648029545.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
         </is>
       </c>
     </row>
@@ -2182,38 +2141,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t>南昌·全职高手only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.13 10:00-02.13 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>22.33</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
         </is>
       </c>
     </row>
@@ -2223,38 +2182,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -2269,33 +2228,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -2310,33 +2269,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>136</v>
+        <v>1342</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -2351,33 +2310,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1319</v>
+        <v>1576</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -2392,33 +2351,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1562</v>
+        <v>346</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -2433,33 +2392,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>343</v>
+        <v>443</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2474,33 +2433,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>431</v>
-      </c>
-      <c r="G10" t="n">
-        <v>50</v>
+        <v>182</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2510,40 +2471,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>182</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>177</v>
+      </c>
+      <c r="G11" t="n">
+        <v>45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -2558,33 +2517,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -2599,33 +2558,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -2635,38 +2594,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -2681,33 +2640,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>285</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -2717,38 +2676,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -2763,33 +2722,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -2804,33 +2763,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>331</v>
+        <v>1771</v>
       </c>
       <c r="G18" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -2840,38 +2799,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1763</v>
+        <v>74</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -2886,33 +2845,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -2922,38 +2881,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2963,38 +2922,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>179</v>
+        <v>697</v>
       </c>
       <c r="G22" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -3009,33 +2968,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>686</v>
-      </c>
-      <c r="G23" t="n">
-        <v>65</v>
+        <v>304</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -3045,40 +3006,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>304</v>
+        <v>347</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3054,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3103,25 +3064,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>345</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4279</v>
+      </c>
+      <c r="G25" t="n">
+        <v>65</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -3136,33 +3095,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4245</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -3177,33 +3136,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>292</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -3213,38 +3172,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>286</v>
+        <v>1125</v>
       </c>
       <c r="G28" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -3254,38 +3213,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1113</v>
+        <v>495</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -3295,38 +3254,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>495</v>
+        <v>46</v>
       </c>
       <c r="G30" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -3341,33 +3300,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>46</v>
+        <v>635</v>
       </c>
       <c r="G31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -3377,38 +3336,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>614</v>
+        <v>24</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -3423,33 +3382,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>23</v>
+        <v>326</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -3464,33 +3423,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>310</v>
+        <v>50</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -3500,38 +3459,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="G35" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -3546,72 +3505,31 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="G36" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>14</v>
-      </c>
-      <c r="G37" t="n">
-        <v>60</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
         <v>22.33</v>
@@ -545,7 +545,7 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G4" t="n">
         <v>35</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1342</v>
+        <v>1351</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1576</v>
+        <v>1584</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G11" t="n">
         <v>45</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G17" t="n">
         <v>40</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G21" t="n">
         <v>40</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4279</v>
+        <v>4295</v>
       </c>
       <c r="G25" t="n">
         <v>65</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G27" t="n">
         <v>30</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G29" t="n">
         <v>45</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>635</v>
+        <v>650</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G34" t="n">
         <v>65</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="G35" t="n">
         <v>55</v>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
         <v>22.33</v>
@@ -2163,7 +2163,7 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G4" t="n">
         <v>35</v>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1342</v>
+        <v>1351</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1576</v>
+        <v>1584</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G11" t="n">
         <v>45</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G17" t="n">
         <v>40</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G21" t="n">
         <v>40</v>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4279</v>
+        <v>4295</v>
       </c>
       <c r="G25" t="n">
         <v>65</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G27" t="n">
         <v>30</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G29" t="n">
         <v>45</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>635</v>
+        <v>650</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G34" t="n">
         <v>65</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="G35" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -569,33 +569,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>103</v>
+        <v>1375</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>139</v>
+        <v>1606</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,33 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1351</v>
+        <v>352</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1584</v>
+        <v>464</v>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>348</v>
-      </c>
-      <c r="G8" t="n">
-        <v>50</v>
+        <v>182</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>451</v>
+        <v>190</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,40 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>182</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>167</v>
+      </c>
+      <c r="G10" t="n">
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>182</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="G12" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -935,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>289</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>323</v>
+        <v>1786</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>334</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
         <v>40</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1773</v>
+        <v>110</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>74</v>
+        <v>183</v>
       </c>
       <c r="G19" t="n">
         <v>40</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>706</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>182</v>
-      </c>
-      <c r="G21" t="n">
-        <v>40</v>
+        <v>304</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1306,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>702</v>
-      </c>
-      <c r="G22" t="n">
-        <v>65</v>
+        <v>349</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1345,40 +1349,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>304</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4324</v>
+      </c>
+      <c r="G23" t="n">
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1393,35 +1395,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>348</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1436,33 +1436,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4295</v>
+        <v>301</v>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1472,38 +1472,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>1145</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1513,38 +1513,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>295</v>
+        <v>500</v>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1554,38 +1554,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1132</v>
+        <v>46</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1595,38 +1595,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>497</v>
+        <v>676</v>
       </c>
       <c r="G29" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1636,38 +1636,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1677,38 +1677,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>650</v>
+        <v>339</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1737,19 +1737,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1759,38 +1759,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>328</v>
+        <v>176</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1800,118 +1800,36 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="G34" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>168</v>
-      </c>
-      <c r="G35" t="n">
-        <v>55</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>14</v>
-      </c>
-      <c r="G36" t="n">
-        <v>60</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -2046,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2100,38 +2018,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赣州·宅舞联萌·随舞动漫派对（免费活动)</t>
+          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金岭东大道新都汇西侧约100米 万达广场</t>
+          <t>平安大道 麋鹿LiveHose</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.12 14:00-02.13 19:00</t>
+          <t>2024.02.14 09:30-02.15 17:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>22.33</v>
+        <v>35</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81540</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5gLDYtbv1706608938962.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
         </is>
       </c>
     </row>
@@ -2141,38 +2059,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·全职高手only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>龙蟠街666号融创茂1层 融创茂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.13 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80750</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kgNI2Efz1706261620244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
         </is>
       </c>
     </row>
@@ -2187,33 +2105,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>南昌·龙年动漫展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>103</v>
+        <v>1375</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
         </is>
       </c>
     </row>
@@ -2228,33 +2146,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>吉安·COMIC LIFE 次元假日03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 09:30-02.14 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>139</v>
+        <v>1606</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
         </is>
       </c>
     </row>
@@ -2269,33 +2187,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>宜春·第三十届静卿国风动漫新春盛典</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.14 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1351</v>
+        <v>352</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
         </is>
       </c>
     </row>
@@ -2310,33 +2228,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1584</v>
+        <v>464</v>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2351,33 +2269,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>赣州·国乙ONLY（取消）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>八一四大道18号 纽豪花园酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>348</v>
-      </c>
-      <c r="G8" t="n">
-        <v>50</v>
+        <v>182</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2387,38 +2307,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>451</v>
+        <v>190</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -2428,40 +2348,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>182</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>167</v>
+      </c>
+      <c r="G10" t="n">
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -2476,12 +2394,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2490,19 +2408,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>182</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -2512,38 +2430,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="G12" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -2553,38 +2471,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>289</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -2594,38 +2512,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -2635,38 +2553,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -2681,33 +2599,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>323</v>
+        <v>1786</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -2717,38 +2635,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>334</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
         <v>40</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -2758,38 +2676,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1773</v>
+        <v>110</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -2799,38 +2717,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>74</v>
+        <v>183</v>
       </c>
       <c r="G19" t="n">
         <v>40</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2840,38 +2758,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>706</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -2881,38 +2799,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>182</v>
-      </c>
-      <c r="G21" t="n">
-        <v>40</v>
+        <v>304</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -2922,38 +2842,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>702</v>
-      </c>
-      <c r="G22" t="n">
-        <v>65</v>
+        <v>349</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -2963,40 +2885,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>304</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4324</v>
+      </c>
+      <c r="G23" t="n">
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -3011,35 +2931,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>348</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -3054,33 +2972,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4295</v>
+        <v>301</v>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -3090,38 +3008,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>1145</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -3131,38 +3049,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>295</v>
+        <v>500</v>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -3172,38 +3090,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1132</v>
+        <v>46</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -3213,38 +3131,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>497</v>
+        <v>676</v>
       </c>
       <c r="G29" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -3254,38 +3172,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -3295,38 +3213,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>650</v>
+        <v>339</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3259,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3355,19 +3273,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -3377,38 +3295,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>328</v>
+        <v>176</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -3418,118 +3336,36 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="G34" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>168</v>
-      </c>
-      <c r="G35" t="n">
-        <v>55</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>14</v>
-      </c>
-      <c r="G36" t="n">
-        <v>60</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1606</v>
+        <v>1618</v>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G9" t="n">
         <v>45</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G12" t="n">
         <v>40</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1786</v>
+        <v>1793</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G18" t="n">
         <v>30</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4324</v>
+        <v>4333</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" t="n">
         <v>10</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G25" t="n">
         <v>30</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G28" t="n">
         <v>55</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G33" t="n">
         <v>55</v>
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1606</v>
+        <v>1619</v>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G9" t="n">
         <v>45</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G12" t="n">
         <v>40</v>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1786</v>
+        <v>1794</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G18" t="n">
         <v>30</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4324</v>
+        <v>4333</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" t="n">
         <v>10</v>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G25" t="n">
         <v>30</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="G27" t="n">
         <v>45</v>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G28" t="n">
         <v>55</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G33" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1385</v>
+        <v>1397</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1618</v>
+        <v>471</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>356</v>
+        <v>203</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>468</v>
+        <v>168</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -728,40 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>182</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="G8" t="n">
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -812,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>167</v>
+        <v>298</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>340</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>123</v>
+        <v>338</v>
       </c>
       <c r="G12" t="n">
         <v>40</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>290</v>
+        <v>1811</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -976,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>330</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>334</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1793</v>
+        <v>184</v>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>712</v>
       </c>
       <c r="G17" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1138,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>111</v>
-      </c>
-      <c r="G18" t="n">
-        <v>30</v>
+        <v>304</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>183</v>
-      </c>
-      <c r="G19" t="n">
-        <v>40</v>
+        <v>349</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1224,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>707</v>
+        <v>4351</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1263,40 +1265,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>304</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1306,40 +1306,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>349</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>310</v>
+      </c>
+      <c r="G22" t="n">
+        <v>30</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1349,38 +1347,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4333</v>
+        <v>1168</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1390,38 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>507</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1431,38 +1429,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>306</v>
+        <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1472,38 +1470,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1150</v>
+        <v>715</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1513,38 +1511,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>503</v>
+        <v>26</v>
       </c>
       <c r="G27" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1554,38 +1552,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>47</v>
+        <v>366</v>
       </c>
       <c r="G28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1595,38 +1593,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>692</v>
+        <v>52</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1636,38 +1634,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1677,159 +1675,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>348</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>51</v>
-      </c>
-      <c r="G32" t="n">
-        <v>65</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>180</v>
-      </c>
-      <c r="G33" t="n">
-        <v>55</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>16</v>
-      </c>
-      <c r="G34" t="n">
-        <v>60</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1964,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2018,7 +1893,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2037,7 +1912,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
@@ -2059,7 +1934,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2100,7 +1975,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2119,7 +1994,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1385</v>
+        <v>1397</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2141,38 +2016,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>吉安·COMIC LIFE 次元假日03</t>
+          <t>江西·第二十一届九江ACJJ国际动漫展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>东塘大道与阳明西路交叉路口往西约240米 吉安国际会展中心</t>
+          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.14 18:00</t>
+          <t>2024.02.14 09:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1619</v>
+        <v>471</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80305</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/gUyU7wgj1703754978855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2182,38 +2057,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>宜春·第三十届静卿国风动漫新春盛典</t>
+          <t>萍乡·au7新年国漫展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宜阳大道19号(交通银行旁) 宜春安缦文华酒店</t>
+          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>356</v>
+        <v>203</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80802</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Pq8w7EsS1705048754533.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
         </is>
       </c>
     </row>
@@ -2223,38 +2098,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>南门口地一大道下沉广场 漫库书店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.15 11:00-02.15 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>468</v>
+        <v>168</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
         </is>
       </c>
     </row>
@@ -2264,40 +2139,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>赣州·国乙ONLY（取消）</t>
+          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>八一四大道18号 纽豪花园酒店</t>
+          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>182</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>80</v>
+      </c>
+      <c r="G8" t="n">
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79487</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Rhqex68Z1701935089796.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
         </is>
       </c>
     </row>
@@ -2307,38 +2180,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -2348,38 +2221,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>167</v>
+        <v>298</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -2389,38 +2262,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>340</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -2430,38 +2303,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>123</v>
+        <v>338</v>
       </c>
       <c r="G12" t="n">
         <v>40</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -2471,38 +2344,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>290</v>
+        <v>1811</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -2512,38 +2385,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>330</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -2553,38 +2426,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>奉新·COP动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>334</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -2594,38 +2467,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1794</v>
+        <v>184</v>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2635,38 +2508,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>712</v>
       </c>
       <c r="G17" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -2676,38 +2549,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>111</v>
-      </c>
-      <c r="G18" t="n">
-        <v>30</v>
+        <v>304</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -2717,38 +2592,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>183</v>
-      </c>
-      <c r="G19" t="n">
-        <v>40</v>
+        <v>349</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -2758,38 +2635,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>707</v>
+        <v>4351</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -2799,40 +2676,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>304</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -2842,40 +2717,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>349</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>310</v>
+      </c>
+      <c r="G22" t="n">
+        <v>30</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -2885,38 +2758,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4333</v>
+        <v>1168</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -2926,38 +2799,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>507</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -2967,38 +2840,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>306</v>
+        <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -3008,38 +2881,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1150</v>
+        <v>715</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -3049,38 +2922,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>503</v>
+        <v>26</v>
       </c>
       <c r="G27" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -3090,38 +2963,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>47</v>
+        <v>366</v>
       </c>
       <c r="G28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -3131,38 +3004,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>692</v>
+        <v>52</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -3172,38 +3045,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -3213,159 +3086,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>348</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>51</v>
-      </c>
-      <c r="G32" t="n">
-        <v>65</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>180</v>
-      </c>
-      <c r="G33" t="n">
-        <v>55</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>16</v>
-      </c>
-      <c r="G34" t="n">
-        <v>60</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -706,10 +706,12 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>168</v>
-      </c>
-      <c r="G7" t="n">
-        <v>48</v>
+        <v>169</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -750,7 +752,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G9" t="n">
         <v>40</v>
@@ -829,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -870,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -911,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G12" t="n">
         <v>40</v>
@@ -952,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1811</v>
+        <v>1822</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -1116,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1200,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1243,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4351</v>
+        <v>4362</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1284,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" t="n">
         <v>10</v>
@@ -1325,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="G22" t="n">
         <v>30</v>
@@ -1366,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1168</v>
+        <v>1179</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G24" t="n">
         <v>45</v>
@@ -1448,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -1489,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>715</v>
+        <v>732</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1571,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1653,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G30" t="n">
         <v>55</v>
@@ -1912,7 +1914,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
@@ -1994,7 +1996,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2076,10 +2078,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2117,10 +2119,12 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>168</v>
-      </c>
-      <c r="G7" t="n">
-        <v>48</v>
+        <v>169</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2161,7 +2165,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2199,7 +2203,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G9" t="n">
         <v>40</v>
@@ -2240,7 +2244,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2281,7 +2285,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -2322,7 +2326,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G12" t="n">
         <v>40</v>
@@ -2363,7 +2367,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1811</v>
+        <v>1822</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -2527,7 +2531,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -2611,7 +2615,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2654,7 +2658,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4351</v>
+        <v>4362</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -2695,7 +2699,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" t="n">
         <v>10</v>
@@ -2736,7 +2740,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="G22" t="n">
         <v>30</v>
@@ -2777,7 +2781,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1168</v>
+        <v>1179</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -2818,7 +2822,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G24" t="n">
         <v>45</v>
@@ -2859,7 +2863,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" t="n">
         <v>55</v>
@@ -2900,7 +2904,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>715</v>
+        <v>732</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -2982,7 +2986,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3064,7 +3068,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G30" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>142</v>
+        <v>303</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1398</v>
+        <v>349</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>471</v>
+        <v>343</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.15</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>207</v>
+        <v>1837</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -687,40 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.15</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>169</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -730,38 +728,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.15</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
-      </c>
-      <c r="G8" t="n">
-        <v>65</v>
+        <v>113</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="G9" t="n">
         <v>40</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>300</v>
+        <v>722</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +853,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>342</v>
-      </c>
-      <c r="G11" t="n">
-        <v>55</v>
+        <v>304</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +896,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>341</v>
-      </c>
-      <c r="G12" t="n">
-        <v>40</v>
+        <v>353</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -935,38 +939,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1822</v>
+        <v>4397</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -976,38 +980,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1021,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
+        <v>323</v>
       </c>
       <c r="G15" t="n">
         <v>30</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>184</v>
+        <v>1191</v>
       </c>
       <c r="G16" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1103,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>715</v>
+        <v>511</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,40 +1144,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>304</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1183,40 +1185,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>351</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>757</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1226,38 +1226,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4362</v>
+        <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1267,38 +1267,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>396</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1308,38 +1308,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>316</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1349,38 +1349,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1179</v>
+        <v>202</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1390,323 +1390,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>509</v>
+        <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024.03.16</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>49</v>
-      </c>
-      <c r="G25" t="n">
-        <v>55</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2024.03.16</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>732</v>
-      </c>
-      <c r="G26" t="n">
-        <v>60</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024.03.23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>上饶·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>五三东大道42号 回禾酒店</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>26</v>
-      </c>
-      <c r="G27" t="n">
-        <v>60</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024.03.23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>381</v>
-      </c>
-      <c r="G28" t="n">
-        <v>60</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2024.03.23</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>52</v>
-      </c>
-      <c r="G29" t="n">
-        <v>65</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>191</v>
-      </c>
-      <c r="G30" t="n">
-        <v>55</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>16</v>
-      </c>
-      <c r="G31" t="n">
-        <v>60</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1841,7 +1554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,38 +1608,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 赣州·十万伏特·2024次元交流会（冬）</t>
+          <t>上高·星语动漫嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>平安大道 麋鹿LiveHose</t>
+          <t>镜山大道2号 迎宾馆大酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.14 09:30-02.15 17:30</t>
+          <t>2024.02.16 09:30-02.16 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mKDiDPv31705921109896.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
         </is>
       </c>
     </row>
@@ -1936,38 +1649,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>龙蟠街666号融创茂1层 融创茂</t>
+          <t>南龙蟠街666号 融创茂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>142</v>
+        <v>303</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80784</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/iNAvP52t1705039345817.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
         </is>
       </c>
     </row>
@@ -1977,38 +1690,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·龙年动漫展</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1398</v>
+        <v>349</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80525</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ezt7koZo1704444854691.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -2018,38 +1731,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江西·第二十一届九江ACJJ国际动漫展</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>体育路九江市体育中心-体育馆 九江市体育中心</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>471</v>
+        <v>343</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81015</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HD1sIIY21705557926335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -2059,38 +1772,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.15</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>萍乡·au7新年国漫展</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>建设西路钻石公寓西南侧60米 智博篮球馆</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>207</v>
+        <v>1837</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80790</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LiamxFS81705481738724.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -2100,40 +1813,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.15</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>赣州·明日方舟ONLY大炎新岁同好交流茶话会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南门口地一大道下沉广场 漫库书店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.15 11:00-02.15 18:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>169</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78689</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/T1Y8Iju31700621742031.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -2143,38 +1854,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.15</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>鹰潭·ADO7新年 原·星·蔚蓝 主题展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南站路锦都金源酒店18楼 锦都金源酒店</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.15 10:00-02.15 17:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
-      </c>
-      <c r="G8" t="n">
-        <v>65</v>
+        <v>113</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6yeUmiu11705646392215.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -2184,38 +1897,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="G9" t="n">
         <v>40</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2225,38 +1938,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>300</v>
+        <v>722</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -2266,38 +1979,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>342</v>
-      </c>
-      <c r="G11" t="n">
-        <v>55</v>
+        <v>304</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -2307,38 +2022,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>341</v>
-      </c>
-      <c r="G12" t="n">
-        <v>40</v>
+        <v>353</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -2348,38 +2065,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1822</v>
+        <v>4397</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -2389,38 +2106,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -2430,38 +2147,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
+        <v>323</v>
       </c>
       <c r="G15" t="n">
         <v>30</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -2471,38 +2188,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>184</v>
+        <v>1191</v>
       </c>
       <c r="G16" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -2512,38 +2229,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>715</v>
+        <v>511</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -2553,40 +2270,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>304</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -2596,40 +2311,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>351</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>757</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -2639,38 +2352,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4362</v>
+        <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -2680,38 +2393,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>396</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2721,38 +2434,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>316</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -2762,38 +2475,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1179</v>
+        <v>202</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -2803,323 +2516,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>509</v>
+        <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024.03.16</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>49</v>
-      </c>
-      <c r="G25" t="n">
-        <v>55</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2024.03.16</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>732</v>
-      </c>
-      <c r="G26" t="n">
-        <v>60</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024.03.23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>上饶·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>五三东大道42号 回禾酒店</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>26</v>
-      </c>
-      <c r="G27" t="n">
-        <v>60</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024.03.23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>381</v>
-      </c>
-      <c r="G28" t="n">
-        <v>60</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2024.03.23</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>52</v>
-      </c>
-      <c r="G29" t="n">
-        <v>65</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>191</v>
-      </c>
-      <c r="G30" t="n">
-        <v>55</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>16</v>
-      </c>
-      <c r="G31" t="n">
-        <v>60</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1837</v>
+        <v>1847</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" t="n">
         <v>40</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4397</v>
+        <v>4407</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G15" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1191</v>
+        <v>1205</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G17" t="n">
         <v>45</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1837</v>
+        <v>1847</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" t="n">
         <v>40</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4397</v>
+        <v>4407</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G15" t="n">
         <v>30</v>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1191</v>
+        <v>1205</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G17" t="n">
         <v>45</v>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G23" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>141</v>
+        <v>359</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -569,33 +569,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>351</v>
+        <v>1860</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1847</v>
-      </c>
-      <c r="G6" t="n">
-        <v>50</v>
+        <v>114</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="G7" t="n">
         <v>40</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,40 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>114</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>741</v>
+      </c>
+      <c r="G8" t="n">
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>189</v>
-      </c>
-      <c r="G9" t="n">
-        <v>40</v>
+        <v>305</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +814,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>731</v>
-      </c>
-      <c r="G10" t="n">
-        <v>65</v>
+        <v>357</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -853,40 +857,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>305</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4442</v>
+      </c>
+      <c r="G11" t="n">
+        <v>65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -901,35 +903,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>354</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -944,33 +944,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4407</v>
+        <v>335</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -980,38 +980,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>1228</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1021,38 +1021,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>326</v>
+        <v>519</v>
       </c>
       <c r="G15" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1062,38 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1205</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1103,38 +1103,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>514</v>
+        <v>796</v>
       </c>
       <c r="G17" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1144,38 +1144,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1185,38 +1185,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>778</v>
+        <v>428</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1267,38 +1267,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>408</v>
+        <v>209</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1308,118 +1308,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>206</v>
-      </c>
-      <c r="G23" t="n">
-        <v>55</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>16</v>
-      </c>
-      <c r="G24" t="n">
-        <v>60</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1554,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,38 +1526,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上高·星语动漫嘉年华</t>
+          <t>九江·ACD动漫游戏嘉年华02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>镜山大道2号 迎宾馆大酒店</t>
+          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.16 09:30-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>141</v>
+        <v>359</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80844</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/QCJN9j8h1705306410081.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1649,38 +1567,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·运动番only</t>
+          <t>江西·樟树静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南龙蟠街666号 融创茂</t>
+          <t>樟树市杏佛路89号 银河国际酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 09:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QXLfgq7f1706180123892.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1695,33 +1613,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>351</v>
+        <v>1860</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1731,38 +1649,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1772,38 +1690,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1847</v>
-      </c>
-      <c r="G6" t="n">
-        <v>50</v>
+        <v>114</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1813,38 +1733,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="G7" t="n">
         <v>40</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1854,40 +1774,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>114</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>741</v>
+      </c>
+      <c r="G8" t="n">
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1897,38 +1815,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>189</v>
-      </c>
-      <c r="G9" t="n">
-        <v>40</v>
+        <v>305</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1938,38 +1858,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>731</v>
-      </c>
-      <c r="G10" t="n">
-        <v>65</v>
+        <v>357</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1979,40 +1901,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>305</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4442</v>
+      </c>
+      <c r="G11" t="n">
+        <v>65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -2027,35 +1947,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>354</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -2070,33 +1988,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4407</v>
+        <v>335</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -2106,38 +2024,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>1228</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -2147,38 +2065,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>326</v>
+        <v>519</v>
       </c>
       <c r="G15" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -2188,38 +2106,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1205</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -2229,38 +2147,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>514</v>
+        <v>796</v>
       </c>
       <c r="G17" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -2270,38 +2188,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -2311,38 +2229,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>778</v>
+        <v>428</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2275,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2371,19 +2289,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -2393,38 +2311,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>408</v>
+        <v>209</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -2434,118 +2352,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>206</v>
-      </c>
-      <c r="G23" t="n">
-        <v>55</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>16</v>
-      </c>
-      <c r="G24" t="n">
-        <v>60</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G7" t="n">
         <v>40</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4442</v>
+        <v>4456</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>10</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G15" t="n">
         <v>45</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>796</v>
+        <v>815</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G7" t="n">
         <v>40</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4442</v>
+        <v>4456</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>10</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G15" t="n">
         <v>45</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>796</v>
+        <v>815</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G21" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,33 +487,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>367</v>
+        <v>1882</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>360</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1870</v>
-      </c>
-      <c r="G4" t="n">
-        <v>60</v>
+        <v>115</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,40 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>749</v>
+      </c>
+      <c r="G6" t="n">
+        <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +689,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>191</v>
-      </c>
-      <c r="G7" t="n">
-        <v>40</v>
+        <v>304</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +732,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>743</v>
-      </c>
-      <c r="G8" t="n">
-        <v>65</v>
+        <v>359</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -771,40 +775,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>304</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4485</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -819,35 +821,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>357</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -862,33 +862,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4456</v>
+        <v>350</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -898,38 +898,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>1266</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -939,38 +939,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>340</v>
+        <v>528</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -980,38 +980,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1241</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1021,38 +1021,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>521</v>
+        <v>849</v>
       </c>
       <c r="G15" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1062,38 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1103,38 +1103,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>815</v>
+        <v>464</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1163,19 +1163,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1185,38 +1185,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>440</v>
+        <v>229</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1226,118 +1226,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>217</v>
-      </c>
-      <c r="G21" t="n">
-        <v>55</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>19</v>
-      </c>
-      <c r="G22" t="n">
-        <v>60</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1472,7 +1390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1531,33 +1449,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>九江·ACD动漫游戏嘉年华02</t>
+          <t>赣州·第一届喵喵鱼动漫游戏展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>九瑞大道与重庆路交汇处西南角 九江国际会展中心</t>
+          <t>105国道东100米 毅德国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 09:30-02.18 16:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>367</v>
+        <v>1882</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81055</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/7BLpSOEZ1705574359625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
         </is>
       </c>
     </row>
@@ -1567,38 +1485,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>江西·樟树静卿国风动漫文化展览会</t>
+          <t>万载·第七届馨缘动漫文化展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>樟树市杏佛路89号 银河国际酒店</t>
+          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.17 09:00-02.17 17:00</t>
+          <t>2024.02.18 09:30-02.18 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>360</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80795</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/DWQnrbtu1705044465383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
         </is>
       </c>
     </row>
@@ -1608,38 +1526,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>应星北大道482号 金勺宴大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.18 09:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1870</v>
-      </c>
-      <c r="G4" t="n">
-        <v>60</v>
+        <v>115</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
         </is>
       </c>
     </row>
@@ -1649,38 +1569,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1690,40 +1610,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>749</v>
+      </c>
+      <c r="G6" t="n">
+        <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1733,38 +1651,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>191</v>
-      </c>
-      <c r="G7" t="n">
-        <v>40</v>
+        <v>304</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1774,38 +1694,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>743</v>
-      </c>
-      <c r="G8" t="n">
-        <v>65</v>
+        <v>359</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1815,40 +1737,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>304</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4485</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1863,35 +1783,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>357</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1906,33 +1824,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4456</v>
+        <v>350</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1942,38 +1860,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>1266</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1983,38 +1901,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>340</v>
+        <v>529</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -2024,38 +1942,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1241</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -2065,38 +1983,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>521</v>
+        <v>849</v>
       </c>
       <c r="G15" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -2106,38 +2024,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -2147,38 +2065,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>815</v>
+        <v>464</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2111,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2207,19 +2125,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -2229,38 +2147,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>440</v>
+        <v>229</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -2270,118 +2188,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>217</v>
-      </c>
-      <c r="G21" t="n">
-        <v>55</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>19</v>
-      </c>
-      <c r="G22" t="n">
-        <v>60</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -545,7 +545,7 @@
         <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4485</v>
+        <v>4506</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1266</v>
+        <v>1285</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>849</v>
+        <v>872</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1507,7 +1507,7 @@
         <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4485</v>
+        <v>4506</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
         <v>10</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1266</v>
+        <v>1285</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>849</v>
+        <v>872</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1885</v>
+        <v>197</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>764</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,26 +564,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>115</v>
+        <v>305</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -592,12 +592,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +607,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>195</v>
-      </c>
-      <c r="G5" t="n">
-        <v>40</v>
+        <v>361</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -648,38 +650,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>760</v>
+        <v>4534</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -689,40 +691,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>305</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -737,35 +737,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>361</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>365</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -775,38 +773,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4506</v>
+        <v>1301</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -816,38 +814,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>536</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -857,38 +855,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>355</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -898,38 +896,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1285</v>
+        <v>895</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -939,38 +937,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>534</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -980,38 +978,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>500</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1021,38 +1019,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>872</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1062,38 +1060,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>236</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1103,159 +1101,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>481</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2024.03.23</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>54</v>
-      </c>
-      <c r="G18" t="n">
-        <v>65</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>230</v>
-      </c>
-      <c r="G19" t="n">
-        <v>55</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>21</v>
-      </c>
-      <c r="G20" t="n">
-        <v>60</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1390,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1444,38 +1319,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赣州·第一届喵喵鱼动漫游戏展</t>
+          <t>江西·高安首届静卿国风动漫文化展览会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>105国道东100米 毅德国际会展中心</t>
+          <t>华林中路606号 华鼎国际大酒店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 09:30-02.18 16:00</t>
+          <t>2024.02.20 09:00-02.20 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1885</v>
+        <v>197</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/KXRHxTLL1699521247861.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
         </is>
       </c>
     </row>
@@ -1485,38 +1360,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>万载·第七届馨缘动漫文化展</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>康乐街道阳乐大道217号 龙凤大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.18 09:30-02.18 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>764</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/6ZDl6Oou1705487204077.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1526,26 +1401,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.18</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>奉新·COP动漫游戏嘉年华1.0（取消）</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>应星北大道482号 金勺宴大酒店</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.18 09:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>115</v>
+        <v>305</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1554,12 +1429,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78259</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/yqw3kAkh1699597195072.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1569,38 +1444,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>195</v>
-      </c>
-      <c r="G5" t="n">
-        <v>40</v>
+        <v>361</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1610,38 +1487,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>760</v>
+        <v>4534</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1651,40 +1528,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>305</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1699,35 +1574,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>361</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>365</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1737,38 +1610,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4506</v>
+        <v>1301</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1778,38 +1651,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>536</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
         </is>
       </c>
     </row>
@@ -1819,38 +1692,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>355</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1860,38 +1733,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1285</v>
+        <v>895</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1901,38 +1774,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>534</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1942,38 +1815,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>500</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1983,38 +1856,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>872</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -2024,38 +1897,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>236</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -2065,159 +1938,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>481</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2024.03.23</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>南昌·原X穹X崩only</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>54</v>
-      </c>
-      <c r="G18" t="n">
-        <v>65</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>230</v>
-      </c>
-      <c r="G19" t="n">
-        <v>55</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>21</v>
-      </c>
-      <c r="G20" t="n">
-        <v>60</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4534</v>
+        <v>4553</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1301</v>
+        <v>1316</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4534</v>
+        <v>4553</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1301</v>
+        <v>1316</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>772</v>
+        <v>1027</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4553</v>
+        <v>4577</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1316</v>
+        <v>1332</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>541</v>
+        <v>883</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -845,7 +845,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>772</v>
+        <v>1027</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4553</v>
+        <v>4577</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1316</v>
+        <v>1332</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>541</v>
+        <v>883</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ae5G3ouV1706092057911.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1027</v>
+        <v>1068</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4577</v>
+        <v>4587</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1332</v>
+        <v>1341</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>944</v>
+        <v>970</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1027</v>
+        <v>1068</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4577</v>
+        <v>4587</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1332</v>
+        <v>1341</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>944</v>
+        <v>970</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>203</v>
+        <v>1074</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -528,33 +528,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1068</v>
-      </c>
-      <c r="G3" t="n">
-        <v>65</v>
+        <v>306</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,40 +566,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -612,7 +614,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -622,25 +624,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>363</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4617</v>
+      </c>
+      <c r="G5" t="n">
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -655,33 +655,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4587</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -696,33 +696,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>387</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -732,38 +732,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>381</v>
+        <v>1367</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,38 +773,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1341</v>
+        <v>906</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +814,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>889</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -860,33 +860,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>54</v>
+        <v>1045</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -896,38 +896,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -942,33 +942,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>572</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -983,33 +983,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>541</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1024,33 +1024,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1319,38 +1319,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.20</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>江西·高安首届静卿国风动漫文化展览会</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>华林中路606号 华鼎国际大酒店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.20 09:00-02.20 17:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>203</v>
+        <v>1074</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kcU6CEz91705040408216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1365,33 +1365,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1068</v>
-      </c>
-      <c r="G3" t="n">
-        <v>65</v>
+        <v>306</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1401,40 +1403,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1451,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1459,25 +1461,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>363</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4617</v>
+      </c>
+      <c r="G5" t="n">
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1492,33 +1492,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4587</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1533,33 +1533,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>387</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1569,38 +1569,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>381</v>
+        <v>1367</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1610,38 +1610,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1341</v>
+        <v>906</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -1651,38 +1651,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>889</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1697,33 +1697,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>54</v>
+        <v>1045</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1733,38 +1733,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1779,33 +1779,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>572</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1820,33 +1820,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>541</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1861,33 +1861,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4617</v>
+        <v>4635</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1045</v>
+        <v>1075</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4617</v>
+        <v>4635</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1045</v>
+        <v>1075</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,10 +501,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1077</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
+        <v>1087</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -585,7 +587,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -628,7 +630,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4635</v>
+        <v>4650</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -710,7 +712,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -751,7 +753,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -792,7 +794,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -874,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1075</v>
+        <v>1120</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -956,10 +958,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1038,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1060,38 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>218</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1106,31 +1108,72 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>南昌·CM01动漫游戏博览会</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024.03.30 10:00-03.31 17:00</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>273</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024.03.30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>23</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>60</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1265,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1338,10 +1381,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1077</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
+        <v>1087</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1422,7 +1467,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1465,7 +1510,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4635</v>
+        <v>4650</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -1547,7 +1592,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -1588,7 +1633,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1629,7 +1674,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1711,7 +1756,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1075</v>
+        <v>1120</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -1793,10 +1838,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1875,7 +1920,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1897,38 +1942,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>218</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1943,31 +1988,72 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>南昌·CM01动漫游戏博览会</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024.03.30 10:00-03.31 17:00</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>273</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024.03.30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>23</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>60</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4650</v>
+        <v>4664</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1385</v>
+        <v>1398</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1120</v>
+        <v>1150</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="G13" t="n">
         <v>58.5</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
         <v>218</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4650</v>
+        <v>4664</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1385</v>
+        <v>1398</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1120</v>
+        <v>1150</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="G13" t="n">
         <v>58.5</v>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
         <v>218</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G17" t="n">
         <v>55</v>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,21 +487,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1094</v>
+        <v>306</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -510,12 +510,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,40 +525,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>306</v>
+        <v>362</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,25 +583,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>362</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4681</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -616,33 +614,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4664</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -657,33 +655,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>399</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -693,38 +691,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>394</v>
+        <v>1406</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -734,38 +732,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1398</v>
+        <v>926</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,38 +773,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>922</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -821,33 +819,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>1188</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -857,38 +855,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1150</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -903,33 +901,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>661</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -944,33 +942,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>636</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>58.5</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -985,33 +983,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1021,38 +1019,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1062,38 +1060,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>282</v>
       </c>
       <c r="G16" t="n">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1108,72 +1106,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>276</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>24</v>
-      </c>
-      <c r="G18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1308,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,21 +1324,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1094</v>
+        <v>306</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1390,12 +1347,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1405,40 +1362,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>306</v>
+        <v>362</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1410,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1463,25 +1420,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>362</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4681</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1496,33 +1451,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4664</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1537,33 +1492,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>399</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1573,38 +1528,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>394</v>
+        <v>1406</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1614,38 +1569,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1398</v>
+        <v>926</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -1655,38 +1610,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>922</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1701,33 +1656,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>1188</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1737,38 +1692,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1150</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1783,33 +1738,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>661</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1824,33 +1779,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>636</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>58.5</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1865,33 +1820,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1901,38 +1856,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1942,38 +1897,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>282</v>
       </c>
       <c r="G16" t="n">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1988,72 +1943,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>276</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>24</v>
-      </c>
-      <c r="G18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,21 +487,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>306</v>
+        <v>1095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -510,12 +510,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,40 +525,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>362</v>
+        <v>306</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,23 +583,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4681</v>
-      </c>
-      <c r="G4" t="n">
-        <v>65</v>
+        <v>363</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -614,33 +616,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>4690</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -655,33 +657,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>399</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,38 +693,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1406</v>
+        <v>404</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -732,38 +734,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>926</v>
+        <v>1413</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,38 +775,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>926</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -819,33 +821,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1188</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -855,38 +857,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>1220</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -901,33 +903,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>661</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
-        <v>58.5</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -942,33 +944,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>682</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>58.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -983,33 +985,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1021,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1060,38 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>218</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1106,31 +1108,72 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>南昌·CM01动漫游戏博览会</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024.03.30 10:00-03.31 17:00</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>284</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024.03.30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>24</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>60</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1265,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1324,21 +1367,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>上饶·囧喵喵次元国风动漫游戏展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>春江北大道19号 博悦宴会艺术中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.23 09:00-02.23 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>306</v>
+        <v>1095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1347,12 +1390,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
         </is>
       </c>
     </row>
@@ -1362,40 +1405,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>362</v>
+        <v>306</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1453,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1420,23 +1463,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4681</v>
-      </c>
-      <c r="G4" t="n">
-        <v>65</v>
+        <v>363</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1451,33 +1496,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>4690</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1492,33 +1537,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>399</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1528,38 +1573,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1406</v>
+        <v>404</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1569,38 +1614,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>926</v>
+        <v>1413</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1610,38 +1655,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>926</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -1656,33 +1701,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1188</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1692,38 +1737,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>1220</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1738,33 +1783,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>661</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
-        <v>58.5</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1779,33 +1824,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>682</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>58.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1820,33 +1865,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1856,38 +1901,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1897,38 +1942,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>218</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1943,31 +1988,72 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>南昌·CM01动漫游戏博览会</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024.03.30 10:00-03.31 17:00</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>284</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024.03.30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>24</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>60</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,21 +487,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1095</v>
+        <v>306</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -510,12 +510,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,40 +525,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>306</v>
+        <v>363</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,25 +583,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>363</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4716</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -616,33 +614,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4690</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -657,33 +655,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>419</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -693,38 +691,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>404</v>
+        <v>1427</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -734,38 +732,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1413</v>
+        <v>933</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,38 +773,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>926</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -821,33 +819,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>1264</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -857,38 +855,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1220</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -903,33 +901,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>944</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -944,33 +942,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>682</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>58.5</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -985,33 +983,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1021,38 +1019,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1062,38 +1060,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>286</v>
       </c>
       <c r="G16" t="n">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1108,72 +1106,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>284</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>24</v>
-      </c>
-      <c r="G18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1308,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,21 +1324,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上饶·囧喵喵次元国风动漫游戏展</t>
+          <t>南昌·国乙only·突破次元计划（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>春江北大道19号 博悦宴会艺术中心</t>
+          <t>高处见美好生活公园 百家喜宴高新店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.23 09:00-02.23 17:00</t>
+          <t>2024.02.23 10:00-02.23 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1095</v>
+        <v>306</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1390,12 +1347,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80240</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/Qwh83wl31703836740097.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1405,40 +1362,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>306</v>
+        <v>363</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1410,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1463,25 +1420,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>363</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4716</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1496,33 +1451,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4690</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1537,33 +1492,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>419</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1573,38 +1528,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>404</v>
+        <v>1427</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1614,38 +1569,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1413</v>
+        <v>933</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -1655,38 +1610,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>926</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1701,33 +1656,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>1264</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1737,38 +1692,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1220</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1783,33 +1738,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>944</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1824,33 +1779,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>682</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>58.5</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1865,33 +1820,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1901,38 +1856,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1942,38 +1897,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>286</v>
       </c>
       <c r="G16" t="n">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1988,72 +1943,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>284</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>24</v>
-      </c>
-      <c r="G18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -540,25 +540,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>363</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4731</v>
+      </c>
+      <c r="G3" t="n">
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -573,33 +571,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4716</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -614,33 +612,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>422</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -650,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>419</v>
+        <v>1435</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1427</v>
+        <v>939</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -732,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>933</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -778,33 +776,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2038</v>
+      </c>
+      <c r="G9" t="n">
         <v>60</v>
       </c>
-      <c r="G9" t="n">
-        <v>55</v>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1264</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -860,33 +858,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>1219</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -901,33 +899,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>944</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>58.5</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -942,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -978,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>291</v>
       </c>
       <c r="G15" t="n">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1065,72 +1063,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>286</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>25</v>
-      </c>
-      <c r="G17" t="n">
-        <v>60</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1265,7 +1222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,40 +1276,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南昌·国乙only·突破次元计划（取消）</t>
+          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>高处见美好生活公园 百家喜宴高新店</t>
+          <t>九龙大道1177号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.23 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80413</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XvmB77wb1704252353395.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1324,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>南昌·第一届Cookie动漫嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1377,25 +1334,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 09:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>363</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4731</v>
+      </c>
+      <c r="G3" t="n">
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
         </is>
       </c>
     </row>
@@ -1410,33 +1365,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>宜春·融荟城难忘今宵汉文化节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>宜阳大道239号 宜春融荟城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.24 18:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4716</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
         </is>
       </c>
     </row>
@@ -1451,33 +1406,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>422</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1487,38 +1442,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>419</v>
+        <v>1435</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1528,38 +1483,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1427</v>
+        <v>939</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -1569,38 +1524,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>933</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1615,33 +1570,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2038</v>
+      </c>
+      <c r="G9" t="n">
         <v>60</v>
       </c>
-      <c r="G9" t="n">
-        <v>55</v>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1651,38 +1606,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1264</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1697,33 +1652,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>1219</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1738,33 +1693,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>944</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>58.5</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1779,33 +1734,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1815,38 +1770,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1856,38 +1811,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>291</v>
       </c>
       <c r="G15" t="n">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1902,72 +1857,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>286</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>25</v>
-      </c>
-      <c r="G17" t="n">
-        <v>60</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,35 +487,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>364</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>430</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -525,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4731</v>
+        <v>1450</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>948</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>422</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -648,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1435</v>
+        <v>2098</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>939</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>1270</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>58.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2038</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,12 +851,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -868,23 +866,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1219</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>58.5</v>
+        <v>218</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -935,159 +933,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2024.03.24</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>34</v>
-      </c>
-      <c r="G14" t="n">
-        <v>218</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>291</v>
-      </c>
-      <c r="G15" t="n">
-        <v>55</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" t="n">
-        <v>60</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1222,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,35 +1156,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南昌·Cookie动漫嘉年华-赵路专场票</t>
+          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>新厂西路315号 陶溪川发布大厅</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 18:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>364</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>430</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81769</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/DhCi2kWe1707123386859.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
         </is>
       </c>
     </row>
@@ -1319,38 +1192,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·第一届Cookie动漫嘉年华</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>九龙大道1177号 南昌绿地国际博览中心</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 09:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4731</v>
+        <v>1450</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81033</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/P994oBkz1705562167665.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1360,38 +1233,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>宜春·融荟城难忘今宵汉文化节</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>宜阳大道239号 宜春融荟城</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.24 18:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>948</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81690</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ldtkc9Sp1706865634128.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -1401,38 +1274,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>422</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1442,38 +1315,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1435</v>
+        <v>2098</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1483,38 +1356,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>939</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1524,38 +1397,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>1270</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>58.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1565,38 +1438,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2038</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1611,33 +1484,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1520,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1662,23 +1535,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1219</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>58.5</v>
+        <v>218</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1688,38 +1561,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1729,159 +1602,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2024.03.24</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>34</v>
-      </c>
-      <c r="G14" t="n">
-        <v>218</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>南昌·CM01动漫游戏博览会</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>291</v>
-      </c>
-      <c r="G15" t="n">
-        <v>55</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" t="n">
-        <v>60</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2098</v>
+        <v>2136</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1270</v>
+        <v>1297</v>
       </c>
       <c r="G8" t="n">
         <v>58.5</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
         <v>218</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2098</v>
+        <v>2136</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1270</v>
+        <v>1297</v>
       </c>
       <c r="G8" t="n">
         <v>58.5</v>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
         <v>218</v>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>434</v>
+        <v>1464</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1456</v>
+        <v>956</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>951</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2186</v>
+      </c>
+      <c r="G5" t="n">
         <v>60</v>
       </c>
-      <c r="G5" t="n">
-        <v>55</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2136</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>1338</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1297</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>58.5</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>321</v>
       </c>
       <c r="G11" t="n">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -897,72 +897,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>309</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G13" t="n">
-        <v>60</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1097,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,38 +1110,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>景德镇·陶溪川×次元文化元宵游园会（ 免费活动）</t>
+          <t>南昌·meeting动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新厂西路315号 陶溪川发布大厅</t>
+          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 18:00</t>
+          <t>2024.03.02 09:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>434</v>
+        <v>1464</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81207</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/nIs2jtUn1707298876430.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1192,38 +1151,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南昌·meeting动漫游戏嘉年华</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南龙潘街666号二楼万达影城斜对面 融创茂啃趣馆</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.03 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1456</v>
+        <v>956</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79555</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/l6GUtggC1706843695971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
         </is>
       </c>
     </row>
@@ -1233,38 +1192,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.09 09:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>951</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1279,33 +1238,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2186</v>
+      </c>
+      <c r="G5" t="n">
         <v>60</v>
       </c>
-      <c r="G5" t="n">
-        <v>55</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,38 +1274,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2136</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1361,33 +1320,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>1338</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1402,33 +1361,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1297</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>58.5</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1443,33 +1402,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1479,38 +1438,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -1520,38 +1479,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·CM01动漫游戏博览会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>321</v>
       </c>
       <c r="G11" t="n">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
         </is>
       </c>
     </row>
@@ -1566,72 +1525,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>309</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024.03.30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>鹰潭·原×铁×崩only</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G13" t="n">
-        <v>60</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1464</v>
+        <v>1477</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2186</v>
+        <v>2224</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1338</v>
+        <v>1366</v>
       </c>
       <c r="G7" t="n">
         <v>58.5</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1464</v>
+        <v>1477</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2186</v>
+        <v>2224</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1338</v>
+        <v>1366</v>
       </c>
       <c r="G7" t="n">
         <v>58.5</v>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G9" t="n">
         <v>58</v>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>

--- a/江西-漫展信息.xlsx
+++ b/江西-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1477</v>
+        <v>1497</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -528,12 +528,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·DSL国风动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>沿江北路69号 瑞颐大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>957</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82107</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QDlumVb41708943318282.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>963</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/hdlmhoLp1708932790894.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2224</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>2290</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1366</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>58.5</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>1407</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>58.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="G10" t="n">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>327</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>218</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/IYLaH7AS1706866218597.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
         </is>
       </c>
     </row>
@@ -897,31 +897,72 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>南昌·CM01动漫游戏博览会</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024.03.30 10:00-03.31 17:00</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>350</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/9cMJMElF1708938074308.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024.03.30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>鹰潭·原×铁×崩only</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>南站路24号 回禾酒店(鹰潭火车站店)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="F13" t="n">
+        <v>26</v>
+      </c>
+      <c r="G13" t="n">
         <v>60</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81097</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/q0AZaXAk1705646244207.jpeg</t>
         </is>
@@ -1056,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1170,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1477</v>
+        <v>1497</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1156,12 +1197,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
+          <t>南昌·DSL国风动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
+          <t>沿江北路69号 瑞颐大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1170,19 +1211,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>957</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82107</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/oM49o66R1708334630235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QDlumVb41708943318282.jpeg</t>
         </is>
       </c>
     </row>
@@ -1192,38 +1233,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
+          <t xml:space="preserve">景德镇·江报国风动漫展 </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>陶阳南路188号 晨枫臻品酒店</t>
+          <t>迎宾大道与寺山路交叉口东200米 陶博城</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.09 09:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>963</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81362</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/hdlmhoLp1708932790894.jpeg</t>
         </is>
       </c>
     </row>
@@ -1238,33 +1279,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>江西·ShiningStaR动漫游戏文化节5th</t>
+          <t>景德镇·原神X崩铁X崩坏动漫展only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
+          <t>陶阳南路188号 晨枫臻品酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2224</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80920</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/IugBckTp1705469476482.png</t>
         </is>
       </c>
     </row>
@@ -1274,38 +1315,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上饶·原×铁×崩only</t>
+          <t>江西·ShiningStaR动漫游戏文化节5th</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>五三东大道42号 回禾酒店</t>
+          <t>高新开发区紫阳大道666号 江西奥林匹克体育中心综合训练馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 09:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>2290</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81792</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/2l16aHBJ1707209383729.jpeg</t>
         </is>
       </c>
     </row>
@@ -1320,33 +1361,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏嘉年华</t>
+          <t>上饶·原×铁×崩only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>五三东大道42号 回禾酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1366</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>58.5</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81103</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pp6c5TsC1705647180602.jpeg</t>
         </is>
       </c>
     </row>
@@ -1361,33 +1402,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南昌·原X穹X崩only</t>
+          <t>南昌·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>丰和北大道299号 新吉花园酒店</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>1407</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>58.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81232</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/NZv97SmS1705912230957.jpeg</t>
         </is>
       </c>
     </row>
@@ -1402,33 +1443,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南昌·运动番only春季集训</t>
+          <t>南昌·原X穹X崩only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
+          <t>丰和北大道299号 新吉花园酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80807</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/rY4v2Opx1705051458246.jpeg</t>
         </is>
       </c>
     </row>
@@ -1438,38 +1479,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
+          <t>南昌·运动番only春季集训</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>八一桥街道青山南路118号 蓝海会展中心</t>
+          <t>创新三路777号 南昌小飞侠章鱼文化体育公园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.24 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="G10" t="n">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81973</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81950</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/zbG5HICL1708504962467.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/bm4uH4qB1708425538357.jpeg</t>
         </is>
       </c>
     </row>
@@ -1479,38 +1520,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南昌·CM01动漫游戏博览会</t>
+          <t>南昌·AP动漫游戏  嘉年华内场票-小N&amp;子音</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>怀玉山大道1315号 南昌绿地国际博览中心</t>
+          <t>八一桥街道青山南路118号 蓝海会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>327</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>218</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81691</t>
+          <t>https://show.bilib